--- a/data/Mu&OffsetData.xlsx
+++ b/data/Mu&OffsetData.xlsx
@@ -205,13 +205,13 @@
     <t>0.69359566,</t>
   </si>
   <si>
-    <t>Cardboard MAE: 0.12204189921964285</t>
+    <t>Cardboard MAE: 0.12099004850535715</t>
   </si>
   <si>
     <t>0.66521889,</t>
   </si>
   <si>
-    <t>Cardboard MRE %: 11.964892080357144</t>
+    <t>Cardboard MRE %: 11.746606651005546</t>
   </si>
   <si>
     <t>0.6785552684,</t>
@@ -700,7 +700,7 @@
     <t>true_tile_mu = 0.69</t>
   </si>
   <si>
-    <t>true_cardboard_mu = 1.02</t>
+    <t>true_cardboard_mu = 1.03</t>
   </si>
   <si>
     <t>true_acrylic_mu = 0.84</t>
@@ -1290,7 +1290,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1329,6 +1329,9 @@
     </xf>
     <xf borderId="12" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="12" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
     <xf borderId="13" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
@@ -4346,7 +4349,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="20" t="s">
         <v>54</v>
       </c>
       <c r="I2" s="1" t="s">
@@ -4354,7 +4357,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="20" t="s">
         <v>56</v>
       </c>
       <c r="I3" s="1" t="s">
@@ -4362,7 +4365,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="20" t="s">
         <v>58</v>
       </c>
       <c r="I4" s="1" t="s">
@@ -4370,7 +4373,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="20" t="s">
         <v>60</v>
       </c>
       <c r="I5" s="1" t="s">
@@ -4378,7 +4381,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="20" t="s">
         <v>62</v>
       </c>
       <c r="I6" s="1" t="s">
@@ -4386,7 +4389,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="20" t="s">
         <v>64</v>
       </c>
       <c r="I7" s="1" t="s">
@@ -4397,7 +4400,7 @@
       <c r="A8" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="20" t="s">
         <v>67</v>
       </c>
       <c r="I8" s="1" t="s">
@@ -4408,7 +4411,7 @@
       <c r="A9" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="20" t="s">
         <v>70</v>
       </c>
       <c r="I9" s="1" t="s">
@@ -4416,7 +4419,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="20" t="s">
         <v>72</v>
       </c>
       <c r="I10" s="1" t="s">
@@ -5413,10 +5416,10 @@
       <c r="K4" s="1">
         <v>0.990763230536271</v>
       </c>
-      <c r="N4" s="20" t="s">
+      <c r="N4" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="O4" s="21"/>
+      <c r="O4" s="22"/>
     </row>
     <row r="5">
       <c r="F5" s="1" t="s">
@@ -6486,14 +6489,14 @@
       <c r="G44" s="1">
         <v>12.898</v>
       </c>
-      <c r="H44" s="22">
+      <c r="H44" s="23">
         <v>1.77076115752053E9</v>
       </c>
       <c r="I44" s="4">
         <f t="shared" si="15"/>
         <v>0.2152712364</v>
       </c>
-      <c r="J44" s="22">
+      <c r="J44" s="23">
         <v>1.0378559732</v>
       </c>
       <c r="K44" s="1">
@@ -6718,7 +6721,7 @@
         <v>11</v>
       </c>
       <c r="K2" s="2"/>
-      <c r="L2" s="23"/>
+      <c r="L2" s="24"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
@@ -6744,7 +6747,7 @@
       <c r="J4" s="1">
         <v>0.7938452464</v>
       </c>
-      <c r="N4" s="24"/>
+      <c r="N4" s="25"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
@@ -6878,7 +6881,7 @@
       <c r="J14" s="1">
         <v>1.0746031465</v>
       </c>
-      <c r="N14" s="24"/>
+      <c r="N14" s="25"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
@@ -6893,9 +6896,9 @@
       <c r="J15" s="1">
         <v>0.7674276654</v>
       </c>
-      <c r="N15" s="24"/>
-      <c r="O15" s="24"/>
-      <c r="P15" s="24"/>
+      <c r="N15" s="25"/>
+      <c r="O15" s="25"/>
+      <c r="P15" s="25"/>
     </row>
     <row r="16">
       <c r="F16" s="1" t="s">
@@ -7238,15 +7241,15 @@
     </row>
     <row r="52">
       <c r="M52" s="2"/>
-      <c r="N52" s="25"/>
-      <c r="O52" s="25"/>
-      <c r="P52" s="25"/>
+      <c r="N52" s="26"/>
+      <c r="O52" s="26"/>
+      <c r="P52" s="26"/>
     </row>
     <row r="53">
       <c r="M53" s="2"/>
-      <c r="N53" s="25"/>
-      <c r="O53" s="25"/>
-      <c r="P53" s="25"/>
+      <c r="N53" s="26"/>
+      <c r="O53" s="26"/>
+      <c r="P53" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -7303,7 +7306,7 @@
       <c r="K1" s="2"/>
     </row>
     <row r="2">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="27" t="s">
         <v>274</v>
       </c>
       <c r="L2" s="2"/>
@@ -7324,8 +7327,8 @@
       <c r="E3" s="1">
         <v>0.8415899703</v>
       </c>
-      <c r="J3" s="27"/>
-      <c r="K3" s="28"/>
+      <c r="J3" s="28"/>
+      <c r="K3" s="29"/>
       <c r="M3" s="1" t="s">
         <v>275</v>
       </c>
@@ -7355,8 +7358,8 @@
       <c r="E4" s="1">
         <v>0.9127304548</v>
       </c>
-      <c r="J4" s="27"/>
-      <c r="K4" s="28"/>
+      <c r="J4" s="28"/>
+      <c r="K4" s="29"/>
       <c r="M4" s="1" t="s">
         <v>281</v>
       </c>
@@ -7386,8 +7389,8 @@
       <c r="E5" s="1">
         <v>0.6960932134</v>
       </c>
-      <c r="J5" s="27"/>
-      <c r="K5" s="28"/>
+      <c r="J5" s="28"/>
+      <c r="K5" s="29"/>
       <c r="M5" s="1" t="s">
         <v>286</v>
       </c>
@@ -7411,7 +7414,7 @@
       <c r="B6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="29">
+      <c r="C6" s="30">
         <v>2.0</v>
       </c>
       <c r="D6" s="1">
@@ -7420,8 +7423,8 @@
       <c r="E6" s="1">
         <v>1.1257118388</v>
       </c>
-      <c r="J6" s="27"/>
-      <c r="K6" s="28"/>
+      <c r="J6" s="28"/>
+      <c r="K6" s="29"/>
       <c r="M6" s="1" t="s">
         <v>291</v>
       </c>
@@ -7451,8 +7454,8 @@
       <c r="E7" s="1">
         <v>0.9801569032</v>
       </c>
-      <c r="J7" s="27"/>
-      <c r="K7" s="28"/>
+      <c r="J7" s="28"/>
+      <c r="K7" s="29"/>
       <c r="M7" s="1" t="s">
         <v>296</v>
       </c>
@@ -7482,8 +7485,8 @@
       <c r="E8" s="1">
         <v>0.711716796</v>
       </c>
-      <c r="J8" s="27"/>
-      <c r="K8" s="28"/>
+      <c r="J8" s="28"/>
+      <c r="K8" s="29"/>
       <c r="M8" s="1" t="s">
         <v>301</v>
       </c>
@@ -7516,8 +7519,8 @@
       <c r="E9" s="1">
         <v>1.1714725596</v>
       </c>
-      <c r="J9" s="27"/>
-      <c r="K9" s="28"/>
+      <c r="J9" s="28"/>
+      <c r="K9" s="29"/>
       <c r="M9" s="1" t="s">
         <v>306</v>
       </c>
@@ -7547,8 +7550,8 @@
       <c r="E10" s="1">
         <v>0.8675244117</v>
       </c>
-      <c r="J10" s="27"/>
-      <c r="K10" s="28"/>
+      <c r="J10" s="28"/>
+      <c r="K10" s="29"/>
       <c r="M10" s="1" t="s">
         <v>310</v>
       </c>
@@ -7578,8 +7581,8 @@
       <c r="E11" s="1">
         <v>0.7205852602</v>
       </c>
-      <c r="J11" s="27"/>
-      <c r="K11" s="28"/>
+      <c r="J11" s="28"/>
+      <c r="K11" s="29"/>
       <c r="M11" s="1" t="s">
         <v>315</v>
       </c>
@@ -7615,8 +7618,8 @@
       <c r="F12" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="J12" s="27"/>
-      <c r="K12" s="28"/>
+      <c r="J12" s="28"/>
+      <c r="K12" s="29"/>
       <c r="M12" s="1" t="s">
         <v>320</v>
       </c>
@@ -7646,8 +7649,8 @@
       <c r="E13" s="1">
         <v>1.0748973615</v>
       </c>
-      <c r="J13" s="27"/>
-      <c r="K13" s="28"/>
+      <c r="J13" s="28"/>
+      <c r="K13" s="29"/>
       <c r="M13" s="1" t="s">
         <v>325</v>
       </c>
@@ -7677,8 +7680,8 @@
       <c r="E14" s="1">
         <v>0.7014588838</v>
       </c>
-      <c r="J14" s="27"/>
-      <c r="K14" s="28"/>
+      <c r="J14" s="28"/>
+      <c r="K14" s="29"/>
       <c r="M14" s="1" t="s">
         <v>330</v>
       </c>
@@ -7711,8 +7714,8 @@
       <c r="E15" s="1">
         <v>1.0939337648</v>
       </c>
-      <c r="J15" s="27"/>
-      <c r="K15" s="28"/>
+      <c r="J15" s="28"/>
+      <c r="K15" s="29"/>
       <c r="M15" s="1" t="s">
         <v>334</v>
       </c>
@@ -7742,8 +7745,8 @@
       <c r="E16" s="1">
         <v>0.9176910204</v>
       </c>
-      <c r="J16" s="27"/>
-      <c r="K16" s="28"/>
+      <c r="J16" s="28"/>
+      <c r="K16" s="29"/>
     </row>
     <row r="17">
       <c r="B17" s="1" t="s">
@@ -7758,8 +7761,8 @@
       <c r="E17" s="1">
         <v>0.7630843658</v>
       </c>
-      <c r="J17" s="27"/>
-      <c r="K17" s="28"/>
+      <c r="J17" s="28"/>
+      <c r="K17" s="29"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
@@ -7777,8 +7780,8 @@
       <c r="E18" s="1">
         <v>1.2232984343</v>
       </c>
-      <c r="J18" s="27"/>
-      <c r="K18" s="28"/>
+      <c r="J18" s="28"/>
+      <c r="K18" s="29"/>
     </row>
     <row r="19">
       <c r="B19" s="1" t="s">
@@ -7793,8 +7796,8 @@
       <c r="E19" s="1">
         <v>0.7205485175</v>
       </c>
-      <c r="J19" s="27"/>
-      <c r="K19" s="28"/>
+      <c r="J19" s="28"/>
+      <c r="K19" s="29"/>
     </row>
     <row r="20">
       <c r="B20" s="1" t="s">
@@ -7809,8 +7812,8 @@
       <c r="E20" s="1">
         <v>0.65954879</v>
       </c>
-      <c r="J20" s="27"/>
-      <c r="K20" s="28"/>
+      <c r="J20" s="28"/>
+      <c r="K20" s="29"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
@@ -7828,8 +7831,8 @@
       <c r="E21" s="1">
         <v>1.2385643507</v>
       </c>
-      <c r="J21" s="27"/>
-      <c r="K21" s="28"/>
+      <c r="J21" s="28"/>
+      <c r="K21" s="29"/>
     </row>
     <row r="22">
       <c r="B22" s="1" t="s">
@@ -7844,14 +7847,14 @@
       <c r="E22" s="1">
         <v>0.9599639196</v>
       </c>
-      <c r="J22" s="27"/>
-      <c r="K22" s="28"/>
-      <c r="M22" s="30"/>
-      <c r="N22" s="30"/>
-      <c r="P22" s="30"/>
-      <c r="S22" s="30"/>
-      <c r="V22" s="31"/>
-      <c r="Y22" s="31"/>
+      <c r="J22" s="28"/>
+      <c r="K22" s="29"/>
+      <c r="M22" s="31"/>
+      <c r="N22" s="31"/>
+      <c r="P22" s="31"/>
+      <c r="S22" s="31"/>
+      <c r="V22" s="32"/>
+      <c r="Y22" s="32"/>
     </row>
     <row r="23">
       <c r="B23" s="1" t="s">
@@ -7866,12 +7869,12 @@
       <c r="E23" s="1">
         <v>0.6950948899</v>
       </c>
-      <c r="J23" s="27"/>
-      <c r="K23" s="28"/>
-      <c r="V23" s="32"/>
-      <c r="W23" s="32"/>
-      <c r="Y23" s="32"/>
-      <c r="Z23" s="32"/>
+      <c r="J23" s="28"/>
+      <c r="K23" s="29"/>
+      <c r="V23" s="33"/>
+      <c r="W23" s="33"/>
+      <c r="Y23" s="33"/>
+      <c r="Z23" s="33"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
@@ -7889,8 +7892,8 @@
       <c r="E24" s="1">
         <v>1.207087062</v>
       </c>
-      <c r="J24" s="27"/>
-      <c r="K24" s="28"/>
+      <c r="J24" s="28"/>
+      <c r="K24" s="29"/>
     </row>
     <row r="25">
       <c r="B25" s="1" t="s">
@@ -7905,8 +7908,8 @@
       <c r="E25" s="1">
         <v>0.9006794133</v>
       </c>
-      <c r="J25" s="27"/>
-      <c r="K25" s="28"/>
+      <c r="J25" s="28"/>
+      <c r="K25" s="29"/>
     </row>
     <row r="26">
       <c r="B26" s="1" t="s">
@@ -7921,8 +7924,8 @@
       <c r="E26" s="1">
         <v>0.6912420848</v>
       </c>
-      <c r="J26" s="27"/>
-      <c r="K26" s="28"/>
+      <c r="J26" s="28"/>
+      <c r="K26" s="29"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
@@ -7940,8 +7943,8 @@
       <c r="E27" s="1">
         <v>1.12737686318637</v>
       </c>
-      <c r="J27" s="27"/>
-      <c r="K27" s="28"/>
+      <c r="J27" s="28"/>
+      <c r="K27" s="29"/>
     </row>
     <row r="28">
       <c r="B28" s="1" t="s">
@@ -7956,8 +7959,8 @@
       <c r="E28" s="1">
         <v>1.10586810208812</v>
       </c>
-      <c r="J28" s="27"/>
-      <c r="K28" s="28"/>
+      <c r="J28" s="28"/>
+      <c r="K28" s="29"/>
     </row>
     <row r="29">
       <c r="B29" s="1" t="s">
@@ -7972,8 +7975,8 @@
       <c r="E29" s="1">
         <v>0.750480501517266</v>
       </c>
-      <c r="J29" s="27"/>
-      <c r="K29" s="28"/>
+      <c r="J29" s="28"/>
+      <c r="K29" s="29"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
@@ -7991,8 +7994,8 @@
       <c r="E30" s="1">
         <v>0.928818455</v>
       </c>
-      <c r="J30" s="27"/>
-      <c r="K30" s="28"/>
+      <c r="J30" s="28"/>
+      <c r="K30" s="29"/>
     </row>
     <row r="31">
       <c r="B31" s="1" t="s">
@@ -8007,8 +8010,8 @@
       <c r="E31" s="1">
         <v>0.6981543221</v>
       </c>
-      <c r="J31" s="27"/>
-      <c r="K31" s="28"/>
+      <c r="J31" s="28"/>
+      <c r="K31" s="29"/>
     </row>
     <row r="32">
       <c r="B32" s="1" t="s">
@@ -8023,8 +8026,8 @@
       <c r="E32" s="1">
         <v>0.6795514235</v>
       </c>
-      <c r="J32" s="27"/>
-      <c r="K32" s="28"/>
+      <c r="J32" s="28"/>
+      <c r="K32" s="29"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
@@ -8042,8 +8045,8 @@
       <c r="E33" s="1">
         <v>1.0654395648</v>
       </c>
-      <c r="J33" s="27"/>
-      <c r="K33" s="28"/>
+      <c r="J33" s="28"/>
+      <c r="K33" s="29"/>
     </row>
     <row r="34">
       <c r="B34" s="1" t="s">
@@ -8058,8 +8061,8 @@
       <c r="E34" s="1">
         <v>0.7520148837</v>
       </c>
-      <c r="J34" s="27"/>
-      <c r="K34" s="28"/>
+      <c r="J34" s="28"/>
+      <c r="K34" s="29"/>
     </row>
     <row r="35">
       <c r="B35" s="1" t="s">
@@ -8074,8 +8077,8 @@
       <c r="E35" s="1">
         <v>0.7371280318</v>
       </c>
-      <c r="J35" s="27"/>
-      <c r="K35" s="28"/>
+      <c r="J35" s="28"/>
+      <c r="K35" s="29"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
@@ -8093,8 +8096,8 @@
       <c r="E36" s="1">
         <v>1.0844269984</v>
       </c>
-      <c r="J36" s="27"/>
-      <c r="K36" s="28"/>
+      <c r="J36" s="28"/>
+      <c r="K36" s="29"/>
     </row>
     <row r="37">
       <c r="B37" s="1" t="s">
@@ -8109,8 +8112,8 @@
       <c r="E37" s="1">
         <v>0.9668405456</v>
       </c>
-      <c r="J37" s="27"/>
-      <c r="K37" s="28"/>
+      <c r="J37" s="28"/>
+      <c r="K37" s="29"/>
     </row>
     <row r="38">
       <c r="B38" s="1" t="s">
@@ -8125,8 +8128,8 @@
       <c r="E38" s="1">
         <v>0.6586842966</v>
       </c>
-      <c r="J38" s="27"/>
-      <c r="K38" s="28"/>
+      <c r="J38" s="28"/>
+      <c r="K38" s="29"/>
     </row>
     <row r="39">
       <c r="A39" s="1" t="s">
@@ -8144,8 +8147,8 @@
       <c r="E39" s="1">
         <v>1.0026714958</v>
       </c>
-      <c r="J39" s="27"/>
-      <c r="K39" s="28"/>
+      <c r="J39" s="28"/>
+      <c r="K39" s="29"/>
     </row>
     <row r="40">
       <c r="B40" s="1" t="s">
@@ -8160,8 +8163,8 @@
       <c r="E40" s="1">
         <v>0.7233920819</v>
       </c>
-      <c r="J40" s="27"/>
-      <c r="K40" s="28"/>
+      <c r="J40" s="28"/>
+      <c r="K40" s="29"/>
     </row>
     <row r="41">
       <c r="B41" s="1" t="s">
@@ -8176,8 +8179,8 @@
       <c r="E41" s="1">
         <v>0.7251524385</v>
       </c>
-      <c r="J41" s="27"/>
-      <c r="K41" s="28"/>
+      <c r="J41" s="28"/>
+      <c r="K41" s="29"/>
     </row>
     <row r="42">
       <c r="A42" s="1" t="s">
@@ -8195,8 +8198,8 @@
       <c r="E42" s="1">
         <v>0.9468346919</v>
       </c>
-      <c r="J42" s="27"/>
-      <c r="K42" s="28"/>
+      <c r="J42" s="28"/>
+      <c r="K42" s="29"/>
     </row>
     <row r="43">
       <c r="B43" s="1" t="s">
@@ -8211,8 +8214,8 @@
       <c r="E43" s="1">
         <v>1.0436262687</v>
       </c>
-      <c r="J43" s="27"/>
-      <c r="K43" s="28"/>
+      <c r="J43" s="28"/>
+      <c r="K43" s="29"/>
     </row>
     <row r="44">
       <c r="B44" s="1" t="s">
@@ -8227,8 +8230,8 @@
       <c r="E44" s="1">
         <v>0.6678314216</v>
       </c>
-      <c r="J44" s="27"/>
-      <c r="K44" s="28"/>
+      <c r="J44" s="28"/>
+      <c r="K44" s="29"/>
     </row>
     <row r="45">
       <c r="A45" s="1" t="s">
@@ -8246,8 +8249,8 @@
       <c r="E45" s="1">
         <v>1.0486527015</v>
       </c>
-      <c r="J45" s="27"/>
-      <c r="K45" s="28"/>
+      <c r="J45" s="28"/>
+      <c r="K45" s="29"/>
     </row>
     <row r="46">
       <c r="B46" s="1" t="s">
@@ -8262,8 +8265,8 @@
       <c r="E46" s="1">
         <v>0.7675737622</v>
       </c>
-      <c r="J46" s="27"/>
-      <c r="K46" s="28"/>
+      <c r="J46" s="28"/>
+      <c r="K46" s="29"/>
     </row>
     <row r="47">
       <c r="B47" s="1" t="s">
@@ -8278,8 +8281,8 @@
       <c r="E47" s="1">
         <v>0.6395216272</v>
       </c>
-      <c r="J47" s="27"/>
-      <c r="K47" s="28"/>
+      <c r="J47" s="28"/>
+      <c r="K47" s="29"/>
     </row>
     <row r="48">
       <c r="A48" s="1" t="s">
@@ -8297,8 +8300,8 @@
       <c r="E48" s="1">
         <v>0.9765088555</v>
       </c>
-      <c r="J48" s="27"/>
-      <c r="K48" s="28"/>
+      <c r="J48" s="28"/>
+      <c r="K48" s="29"/>
     </row>
     <row r="49">
       <c r="B49" s="1" t="s">
@@ -8313,8 +8316,8 @@
       <c r="E49" s="1">
         <v>0.6747166092</v>
       </c>
-      <c r="J49" s="27"/>
-      <c r="K49" s="28"/>
+      <c r="J49" s="28"/>
+      <c r="K49" s="29"/>
     </row>
     <row r="50">
       <c r="B50" s="1" t="s">
@@ -8329,8 +8332,8 @@
       <c r="E50" s="1">
         <v>0.630516063</v>
       </c>
-      <c r="J50" s="27"/>
-      <c r="K50" s="28"/>
+      <c r="J50" s="28"/>
+      <c r="K50" s="29"/>
     </row>
     <row r="51">
       <c r="A51" s="1" t="s">
@@ -8351,8 +8354,8 @@
       <c r="F51" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="J51" s="27"/>
-      <c r="K51" s="28"/>
+      <c r="J51" s="28"/>
+      <c r="K51" s="29"/>
     </row>
     <row r="52">
       <c r="B52" s="1" t="s">
@@ -8367,8 +8370,8 @@
       <c r="E52" s="1">
         <v>0.6826693048</v>
       </c>
-      <c r="J52" s="27"/>
-      <c r="K52" s="28"/>
+      <c r="J52" s="28"/>
+      <c r="K52" s="29"/>
     </row>
     <row r="53">
       <c r="B53" s="1" t="s">
@@ -8383,8 +8386,8 @@
       <c r="E53" s="1">
         <v>0.5967960455</v>
       </c>
-      <c r="J53" s="27"/>
-      <c r="K53" s="28"/>
+      <c r="J53" s="28"/>
+      <c r="K53" s="29"/>
     </row>
     <row r="54">
       <c r="A54" s="1" t="s">
@@ -8402,8 +8405,8 @@
       <c r="E54" s="1">
         <v>0.9142219725</v>
       </c>
-      <c r="J54" s="27"/>
-      <c r="K54" s="28"/>
+      <c r="J54" s="28"/>
+      <c r="K54" s="29"/>
     </row>
     <row r="55">
       <c r="B55" s="1" t="s">
@@ -8418,8 +8421,8 @@
       <c r="E55" s="1">
         <v>0.722906372</v>
       </c>
-      <c r="J55" s="27"/>
-      <c r="K55" s="28"/>
+      <c r="J55" s="28"/>
+      <c r="K55" s="29"/>
     </row>
     <row r="56">
       <c r="B56" s="1" t="s">
@@ -8434,8 +8437,8 @@
       <c r="E56" s="1">
         <v>0.6952665292</v>
       </c>
-      <c r="J56" s="27"/>
-      <c r="K56" s="28"/>
+      <c r="J56" s="28"/>
+      <c r="K56" s="29"/>
     </row>
     <row r="57">
       <c r="A57" s="1" t="s">
@@ -8453,8 +8456,8 @@
       <c r="E57" s="1">
         <v>0.936962369024282</v>
       </c>
-      <c r="J57" s="27"/>
-      <c r="K57" s="28"/>
+      <c r="J57" s="28"/>
+      <c r="K57" s="29"/>
     </row>
     <row r="58">
       <c r="B58" s="1" t="s">
@@ -8469,8 +8472,8 @@
       <c r="E58" s="1">
         <v>1.06170511115125</v>
       </c>
-      <c r="J58" s="27"/>
-      <c r="K58" s="28"/>
+      <c r="J58" s="28"/>
+      <c r="K58" s="29"/>
     </row>
     <row r="59">
       <c r="B59" s="1" t="s">
@@ -8485,8 +8488,8 @@
       <c r="E59" s="1">
         <v>0.699887318630538</v>
       </c>
-      <c r="J59" s="27"/>
-      <c r="K59" s="28"/>
+      <c r="J59" s="28"/>
+      <c r="K59" s="29"/>
     </row>
     <row r="60">
       <c r="A60" s="1" t="s">
@@ -8504,8 +8507,8 @@
       <c r="E60" s="1">
         <v>1.02945181978471</v>
       </c>
-      <c r="J60" s="27"/>
-      <c r="K60" s="28"/>
+      <c r="J60" s="28"/>
+      <c r="K60" s="29"/>
     </row>
     <row r="61">
       <c r="B61" s="1" t="s">
@@ -8520,11 +8523,11 @@
       <c r="E61" s="1">
         <v>0.916437840058194</v>
       </c>
-      <c r="J61" s="27"/>
-      <c r="K61" s="28"/>
+      <c r="J61" s="28"/>
+      <c r="K61" s="29"/>
     </row>
     <row r="62">
-      <c r="A62" s="25"/>
+      <c r="A62" s="26"/>
       <c r="B62" s="1" t="s">
         <v>17</v>
       </c>
@@ -8537,11 +8540,11 @@
       <c r="E62" s="1">
         <v>0.699786398186203</v>
       </c>
-      <c r="J62" s="27"/>
-      <c r="K62" s="28"/>
+      <c r="J62" s="28"/>
+      <c r="K62" s="29"/>
     </row>
     <row r="63">
-      <c r="A63" s="26" t="s">
+      <c r="A63" s="27" t="s">
         <v>338</v>
       </c>
       <c r="C63" s="1" t="s">
@@ -8566,8 +8569,8 @@
       <c r="E64" s="1">
         <v>0.6918024201</v>
       </c>
-      <c r="J64" s="27"/>
-      <c r="K64" s="28"/>
+      <c r="J64" s="28"/>
+      <c r="K64" s="29"/>
     </row>
     <row r="65">
       <c r="B65" s="1" t="s">
@@ -8582,8 +8585,8 @@
       <c r="E65" s="1">
         <v>0.9907632305</v>
       </c>
-      <c r="J65" s="27"/>
-      <c r="K65" s="28"/>
+      <c r="J65" s="28"/>
+      <c r="K65" s="29"/>
     </row>
     <row r="66">
       <c r="B66" s="1" t="s">
@@ -8598,8 +8601,8 @@
       <c r="E66" s="1">
         <v>0.82483737</v>
       </c>
-      <c r="J66" s="27"/>
-      <c r="K66" s="28"/>
+      <c r="J66" s="28"/>
+      <c r="K66" s="29"/>
     </row>
     <row r="67">
       <c r="A67" s="1" t="s">
@@ -8617,8 +8620,8 @@
       <c r="E67" s="1">
         <v>0.6935956635</v>
       </c>
-      <c r="J67" s="27"/>
-      <c r="K67" s="28"/>
+      <c r="J67" s="28"/>
+      <c r="K67" s="29"/>
     </row>
     <row r="68">
       <c r="B68" s="1" t="s">
@@ -8633,8 +8636,8 @@
       <c r="E68" s="1">
         <v>1.0573650168</v>
       </c>
-      <c r="J68" s="27"/>
-      <c r="K68" s="28"/>
+      <c r="J68" s="28"/>
+      <c r="K68" s="29"/>
     </row>
     <row r="69">
       <c r="B69" s="1" t="s">
@@ -8649,8 +8652,8 @@
       <c r="E69" s="1">
         <v>0.9511330905</v>
       </c>
-      <c r="J69" s="27"/>
-      <c r="K69" s="28"/>
+      <c r="J69" s="28"/>
+      <c r="K69" s="29"/>
     </row>
     <row r="70">
       <c r="A70" s="1" t="s">
@@ -8668,8 +8671,8 @@
       <c r="E70" s="1">
         <v>0.6652188953</v>
       </c>
-      <c r="J70" s="27"/>
-      <c r="K70" s="28"/>
+      <c r="J70" s="28"/>
+      <c r="K70" s="29"/>
     </row>
     <row r="71">
       <c r="B71" s="1" t="s">
@@ -8684,8 +8687,8 @@
       <c r="E71" s="1">
         <v>0.9292311212</v>
       </c>
-      <c r="J71" s="27"/>
-      <c r="K71" s="28"/>
+      <c r="J71" s="28"/>
+      <c r="K71" s="29"/>
     </row>
     <row r="72">
       <c r="B72" s="1" t="s">
@@ -8700,8 +8703,8 @@
       <c r="E72" s="1">
         <v>0.9478648152</v>
       </c>
-      <c r="J72" s="27"/>
-      <c r="K72" s="28"/>
+      <c r="J72" s="28"/>
+      <c r="K72" s="29"/>
     </row>
     <row r="73">
       <c r="A73" s="1" t="s">
@@ -8719,8 +8722,8 @@
       <c r="E73" s="1">
         <v>0.6785552684</v>
       </c>
-      <c r="J73" s="27"/>
-      <c r="K73" s="28"/>
+      <c r="J73" s="28"/>
+      <c r="K73" s="29"/>
     </row>
     <row r="74">
       <c r="B74" s="1" t="s">
@@ -8735,8 +8738,8 @@
       <c r="E74" s="1">
         <v>0.8446965494</v>
       </c>
-      <c r="J74" s="27"/>
-      <c r="K74" s="28"/>
+      <c r="J74" s="28"/>
+      <c r="K74" s="29"/>
     </row>
     <row r="75">
       <c r="B75" s="1" t="s">
@@ -8751,8 +8754,8 @@
       <c r="E75" s="1">
         <v>0.7181710076</v>
       </c>
-      <c r="J75" s="27"/>
-      <c r="K75" s="28"/>
+      <c r="J75" s="28"/>
+      <c r="K75" s="29"/>
     </row>
     <row r="76">
       <c r="A76" s="1" t="s">
@@ -8770,8 +8773,8 @@
       <c r="E76" s="1">
         <v>0.7404798108</v>
       </c>
-      <c r="J76" s="27"/>
-      <c r="K76" s="28"/>
+      <c r="J76" s="28"/>
+      <c r="K76" s="29"/>
     </row>
     <row r="77">
       <c r="B77" s="1" t="s">
@@ -8786,8 +8789,8 @@
       <c r="E77" s="1">
         <v>1.0419580617</v>
       </c>
-      <c r="J77" s="27"/>
-      <c r="K77" s="28"/>
+      <c r="J77" s="28"/>
+      <c r="K77" s="29"/>
     </row>
     <row r="78">
       <c r="B78" s="1" t="s">
@@ -8802,8 +8805,8 @@
       <c r="E78" s="1">
         <v>0.6789101833</v>
       </c>
-      <c r="J78" s="27"/>
-      <c r="K78" s="28"/>
+      <c r="J78" s="28"/>
+      <c r="K78" s="29"/>
     </row>
     <row r="79">
       <c r="A79" s="1" t="s">
@@ -8821,8 +8824,8 @@
       <c r="E79" s="1">
         <v>0.722388690672348</v>
       </c>
-      <c r="J79" s="27"/>
-      <c r="K79" s="28"/>
+      <c r="J79" s="28"/>
+      <c r="K79" s="29"/>
     </row>
     <row r="80">
       <c r="B80" s="1" t="s">
@@ -8837,8 +8840,8 @@
       <c r="E80" s="1">
         <v>0.875038589623464</v>
       </c>
-      <c r="J80" s="27"/>
-      <c r="K80" s="28"/>
+      <c r="J80" s="28"/>
+      <c r="K80" s="29"/>
     </row>
     <row r="81">
       <c r="B81" s="1" t="s">
@@ -8853,8 +8856,8 @@
       <c r="E81" s="1">
         <v>1.39046467117004</v>
       </c>
-      <c r="J81" s="27"/>
-      <c r="K81" s="28"/>
+      <c r="J81" s="28"/>
+      <c r="K81" s="29"/>
     </row>
     <row r="82">
       <c r="A82" s="1" t="s">
@@ -8872,8 +8875,8 @@
       <c r="E82" s="1">
         <v>0.6938557598</v>
       </c>
-      <c r="J82" s="27"/>
-      <c r="K82" s="28"/>
+      <c r="J82" s="28"/>
+      <c r="K82" s="29"/>
     </row>
     <row r="83">
       <c r="B83" s="1" t="s">
@@ -8888,8 +8891,8 @@
       <c r="E83" s="1">
         <v>0.8980291949</v>
       </c>
-      <c r="J83" s="27"/>
-      <c r="K83" s="28"/>
+      <c r="J83" s="28"/>
+      <c r="K83" s="29"/>
     </row>
     <row r="84">
       <c r="B84" s="1" t="s">
@@ -8904,8 +8907,8 @@
       <c r="E84" s="1">
         <v>0.7200478942</v>
       </c>
-      <c r="J84" s="27"/>
-      <c r="K84" s="28"/>
+      <c r="J84" s="28"/>
+      <c r="K84" s="29"/>
     </row>
     <row r="85">
       <c r="A85" s="1" t="s">
@@ -8923,8 +8926,8 @@
       <c r="E85" s="1">
         <v>0.6759991876</v>
       </c>
-      <c r="J85" s="27"/>
-      <c r="K85" s="28"/>
+      <c r="J85" s="28"/>
+      <c r="K85" s="29"/>
     </row>
     <row r="86">
       <c r="B86" s="1" t="s">
@@ -8939,8 +8942,8 @@
       <c r="E86" s="1">
         <v>1.0596259539</v>
       </c>
-      <c r="J86" s="27"/>
-      <c r="K86" s="28"/>
+      <c r="J86" s="28"/>
+      <c r="K86" s="29"/>
     </row>
     <row r="87">
       <c r="B87" s="1" t="s">
@@ -8955,8 +8958,8 @@
       <c r="E87" s="1">
         <v>0.7635727213</v>
       </c>
-      <c r="J87" s="27"/>
-      <c r="K87" s="28"/>
+      <c r="J87" s="28"/>
+      <c r="K87" s="29"/>
     </row>
     <row r="88">
       <c r="A88" s="1" t="s">
@@ -8974,8 +8977,8 @@
       <c r="E88" s="1">
         <v>0.617555902263986</v>
       </c>
-      <c r="J88" s="27"/>
-      <c r="K88" s="28"/>
+      <c r="J88" s="28"/>
+      <c r="K88" s="29"/>
     </row>
     <row r="89">
       <c r="B89" s="1" t="s">
@@ -8990,8 +8993,8 @@
       <c r="E89" s="1">
         <v>1.05526514702039</v>
       </c>
-      <c r="J89" s="27"/>
-      <c r="K89" s="28"/>
+      <c r="J89" s="28"/>
+      <c r="K89" s="29"/>
     </row>
     <row r="90">
       <c r="B90" s="1" t="s">
@@ -9006,8 +9009,8 @@
       <c r="E90" s="1">
         <v>0.7068303251794</v>
       </c>
-      <c r="J90" s="27"/>
-      <c r="K90" s="28"/>
+      <c r="J90" s="28"/>
+      <c r="K90" s="29"/>
     </row>
     <row r="91">
       <c r="A91" s="1" t="s">
@@ -9025,8 +9028,8 @@
       <c r="E91" s="1">
         <v>0.648114875180265</v>
       </c>
-      <c r="J91" s="27"/>
-      <c r="K91" s="28"/>
+      <c r="J91" s="28"/>
+      <c r="K91" s="29"/>
     </row>
     <row r="92">
       <c r="B92" s="1" t="s">
@@ -9041,8 +9044,8 @@
       <c r="E92" s="1">
         <v>0.898316619561315</v>
       </c>
-      <c r="J92" s="27"/>
-      <c r="K92" s="28"/>
+      <c r="J92" s="28"/>
+      <c r="K92" s="29"/>
     </row>
     <row r="93">
       <c r="B93" s="1" t="s">
@@ -9057,8 +9060,8 @@
       <c r="E93" s="1">
         <v>0.729357808900581</v>
       </c>
-      <c r="J93" s="27"/>
-      <c r="K93" s="28"/>
+      <c r="J93" s="28"/>
+      <c r="K93" s="29"/>
     </row>
     <row r="94">
       <c r="A94" s="1" t="s">
@@ -9076,8 +9079,8 @@
       <c r="E94" s="1">
         <v>0.6756369776</v>
       </c>
-      <c r="J94" s="27"/>
-      <c r="K94" s="28"/>
+      <c r="J94" s="28"/>
+      <c r="K94" s="29"/>
     </row>
     <row r="95">
       <c r="B95" s="1" t="s">
@@ -9092,8 +9095,8 @@
       <c r="E95" s="1">
         <v>1.0959080646</v>
       </c>
-      <c r="J95" s="27"/>
-      <c r="K95" s="28"/>
+      <c r="J95" s="28"/>
+      <c r="K95" s="29"/>
     </row>
     <row r="96">
       <c r="B96" s="1" t="s">
@@ -9108,10 +9111,10 @@
       <c r="E96" s="1">
         <v>0.774511134</v>
       </c>
-      <c r="J96" s="27"/>
-      <c r="K96" s="28"/>
-      <c r="N96" s="33"/>
-      <c r="O96" s="33"/>
+      <c r="J96" s="28"/>
+      <c r="K96" s="29"/>
+      <c r="N96" s="34"/>
+      <c r="O96" s="34"/>
     </row>
     <row r="97">
       <c r="A97" s="1" t="s">
@@ -9120,7 +9123,7 @@
       <c r="B97" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C97" s="22">
+      <c r="C97" s="23">
         <v>4.0</v>
       </c>
       <c r="D97" s="1">
@@ -9129,10 +9132,10 @@
       <c r="E97" s="1">
         <v>0.7324887419</v>
       </c>
-      <c r="J97" s="27"/>
-      <c r="K97" s="28"/>
-      <c r="N97" s="33"/>
-      <c r="O97" s="33"/>
+      <c r="J97" s="28"/>
+      <c r="K97" s="29"/>
+      <c r="N97" s="34"/>
+      <c r="O97" s="34"/>
     </row>
     <row r="98">
       <c r="B98" s="1" t="s">
@@ -9147,10 +9150,10 @@
       <c r="E98" s="1">
         <v>1.0326041155</v>
       </c>
-      <c r="J98" s="27"/>
-      <c r="K98" s="28"/>
-      <c r="N98" s="33"/>
-      <c r="O98" s="33"/>
+      <c r="J98" s="28"/>
+      <c r="K98" s="29"/>
+      <c r="N98" s="34"/>
+      <c r="O98" s="34"/>
     </row>
     <row r="99">
       <c r="B99" s="1" t="s">
@@ -9165,10 +9168,10 @@
       <c r="E99" s="1">
         <v>0.7585566574</v>
       </c>
-      <c r="J99" s="27"/>
-      <c r="K99" s="28"/>
-      <c r="N99" s="33"/>
-      <c r="O99" s="33"/>
+      <c r="J99" s="28"/>
+      <c r="K99" s="29"/>
+      <c r="N99" s="34"/>
+      <c r="O99" s="34"/>
     </row>
     <row r="100">
       <c r="A100" s="1" t="s">
@@ -9177,7 +9180,7 @@
       <c r="B100" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C100" s="22">
+      <c r="C100" s="23">
         <v>2.0</v>
       </c>
       <c r="D100" s="1">
@@ -9186,10 +9189,10 @@
       <c r="E100" s="1">
         <v>0.6739674954</v>
       </c>
-      <c r="J100" s="27"/>
-      <c r="K100" s="28"/>
-      <c r="N100" s="33"/>
-      <c r="O100" s="33"/>
+      <c r="J100" s="28"/>
+      <c r="K100" s="29"/>
+      <c r="N100" s="34"/>
+      <c r="O100" s="34"/>
     </row>
     <row r="101">
       <c r="B101" s="1" t="s">
@@ -9204,10 +9207,10 @@
       <c r="E101" s="1">
         <v>0.9697900619</v>
       </c>
-      <c r="J101" s="27"/>
-      <c r="K101" s="28"/>
-      <c r="N101" s="33"/>
-      <c r="O101" s="33"/>
+      <c r="J101" s="28"/>
+      <c r="K101" s="29"/>
+      <c r="N101" s="34"/>
+      <c r="O101" s="34"/>
     </row>
     <row r="102">
       <c r="B102" s="1" t="s">
@@ -9222,10 +9225,10 @@
       <c r="E102" s="1">
         <v>1.1288435358</v>
       </c>
-      <c r="J102" s="27"/>
-      <c r="K102" s="28"/>
-      <c r="N102" s="33"/>
-      <c r="O102" s="33"/>
+      <c r="J102" s="28"/>
+      <c r="K102" s="29"/>
+      <c r="N102" s="34"/>
+      <c r="O102" s="34"/>
     </row>
     <row r="103">
       <c r="A103" s="1" t="s">
@@ -9234,7 +9237,7 @@
       <c r="B103" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C103" s="22">
+      <c r="C103" s="23">
         <v>3.0</v>
       </c>
       <c r="D103" s="1">
@@ -9243,10 +9246,10 @@
       <c r="E103" s="1">
         <v>0.6695189558</v>
       </c>
-      <c r="J103" s="27"/>
-      <c r="K103" s="28"/>
-      <c r="N103" s="33"/>
-      <c r="O103" s="33"/>
+      <c r="J103" s="28"/>
+      <c r="K103" s="29"/>
+      <c r="N103" s="34"/>
+      <c r="O103" s="34"/>
     </row>
     <row r="104">
       <c r="B104" s="1" t="s">
@@ -9261,10 +9264,10 @@
       <c r="E104" s="1">
         <v>0.8664588519</v>
       </c>
-      <c r="J104" s="27"/>
-      <c r="K104" s="28"/>
-      <c r="N104" s="33"/>
-      <c r="O104" s="33"/>
+      <c r="J104" s="28"/>
+      <c r="K104" s="29"/>
+      <c r="N104" s="34"/>
+      <c r="O104" s="34"/>
     </row>
     <row r="105">
       <c r="B105" s="1" t="s">
@@ -9273,16 +9276,16 @@
       <c r="C105" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="D105" s="22">
+      <c r="D105" s="23">
         <v>1.77076115752053E9</v>
       </c>
-      <c r="E105" s="22">
+      <c r="E105" s="23">
         <v>1.0378559732</v>
       </c>
-      <c r="J105" s="27"/>
-      <c r="K105" s="28"/>
-      <c r="N105" s="33"/>
-      <c r="O105" s="33"/>
+      <c r="J105" s="28"/>
+      <c r="K105" s="29"/>
+      <c r="N105" s="34"/>
+      <c r="O105" s="34"/>
     </row>
     <row r="106">
       <c r="A106" s="1" t="s">
@@ -9291,7 +9294,7 @@
       <c r="B106" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C106" s="22">
+      <c r="C106" s="23">
         <v>5.0</v>
       </c>
       <c r="D106" s="1">
@@ -9300,10 +9303,10 @@
       <c r="E106" s="1">
         <v>0.7058638883</v>
       </c>
-      <c r="J106" s="27"/>
-      <c r="K106" s="28"/>
-      <c r="N106" s="33"/>
-      <c r="O106" s="33"/>
+      <c r="J106" s="28"/>
+      <c r="K106" s="29"/>
+      <c r="N106" s="34"/>
+      <c r="O106" s="34"/>
     </row>
     <row r="107">
       <c r="B107" s="1" t="s">
@@ -9318,10 +9321,10 @@
       <c r="E107" s="1">
         <v>1.0436391403</v>
       </c>
-      <c r="J107" s="27"/>
-      <c r="K107" s="28"/>
-      <c r="N107" s="33"/>
-      <c r="O107" s="33"/>
+      <c r="J107" s="28"/>
+      <c r="K107" s="29"/>
+      <c r="N107" s="34"/>
+      <c r="O107" s="34"/>
     </row>
     <row r="108">
       <c r="B108" s="1" t="s">
@@ -9336,10 +9339,10 @@
       <c r="E108" s="1">
         <v>0.7070192763</v>
       </c>
-      <c r="J108" s="27"/>
-      <c r="K108" s="28"/>
-      <c r="N108" s="33"/>
-      <c r="O108" s="33"/>
+      <c r="J108" s="28"/>
+      <c r="K108" s="29"/>
+      <c r="N108" s="34"/>
+      <c r="O108" s="34"/>
     </row>
     <row r="109">
       <c r="A109" s="1" t="s">
@@ -9357,8 +9360,8 @@
       <c r="E109" s="1">
         <v>0.6993529493</v>
       </c>
-      <c r="J109" s="27"/>
-      <c r="K109" s="28"/>
+      <c r="J109" s="28"/>
+      <c r="K109" s="29"/>
     </row>
     <row r="110">
       <c r="B110" s="1" t="s">
@@ -9373,8 +9376,8 @@
       <c r="E110" s="1">
         <v>0.8183505199</v>
       </c>
-      <c r="J110" s="27"/>
-      <c r="K110" s="28"/>
+      <c r="J110" s="28"/>
+      <c r="K110" s="29"/>
     </row>
     <row r="111">
       <c r="B111" s="1" t="s">
@@ -9389,18 +9392,18 @@
       <c r="E111" s="1">
         <v>0.7157412862</v>
       </c>
-      <c r="J111" s="27"/>
-      <c r="K111" s="28"/>
+      <c r="J111" s="28"/>
+      <c r="K111" s="29"/>
     </row>
     <row r="112">
-      <c r="A112" s="26" t="s">
+      <c r="A112" s="27" t="s">
         <v>339</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="J112" s="27"/>
-      <c r="K112" s="28"/>
+      <c r="J112" s="28"/>
+      <c r="K112" s="29"/>
     </row>
     <row r="113">
       <c r="A113" s="1" t="s">
@@ -9418,7 +9421,7 @@
       <c r="E113" s="1">
         <v>0.7631135756</v>
       </c>
-      <c r="J113" s="27"/>
+      <c r="J113" s="28"/>
     </row>
     <row r="114">
       <c r="B114" s="1" t="s">
@@ -9433,7 +9436,7 @@
       <c r="E114" s="1">
         <v>0.7938452464</v>
       </c>
-      <c r="J114" s="27"/>
+      <c r="J114" s="28"/>
     </row>
     <row r="115">
       <c r="A115" s="1" t="s">
@@ -9451,7 +9454,7 @@
       <c r="E115" s="1">
         <v>0.7634124267</v>
       </c>
-      <c r="J115" s="27"/>
+      <c r="J115" s="28"/>
     </row>
     <row r="116">
       <c r="B116" s="1" t="s">
@@ -9466,7 +9469,7 @@
       <c r="E116" s="1">
         <v>0.8280248969</v>
       </c>
-      <c r="J116" s="27"/>
+      <c r="J116" s="28"/>
     </row>
     <row r="117">
       <c r="A117" s="1" t="s">
@@ -9487,7 +9490,7 @@
       <c r="F117" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="J117" s="27"/>
+      <c r="J117" s="28"/>
     </row>
     <row r="118">
       <c r="B118" s="1" t="s">
@@ -9502,7 +9505,7 @@
       <c r="E118" s="1">
         <v>1.1734408999</v>
       </c>
-      <c r="J118" s="27"/>
+      <c r="J118" s="28"/>
     </row>
     <row r="119">
       <c r="A119" s="1" t="s">
@@ -9520,7 +9523,7 @@
       <c r="E119" s="1">
         <v>0.7402349295</v>
       </c>
-      <c r="J119" s="27"/>
+      <c r="J119" s="28"/>
     </row>
     <row r="120">
       <c r="B120" s="1" t="s">
@@ -9535,7 +9538,7 @@
       <c r="E120" s="1">
         <v>1.2271572646</v>
       </c>
-      <c r="J120" s="27"/>
+      <c r="J120" s="28"/>
     </row>
     <row r="121">
       <c r="A121" s="1" t="s">
@@ -9553,7 +9556,7 @@
       <c r="E121" s="1">
         <v>0.760669434604679</v>
       </c>
-      <c r="J121" s="27"/>
+      <c r="J121" s="28"/>
     </row>
     <row r="122">
       <c r="B122" s="1" t="s">
@@ -9568,7 +9571,7 @@
       <c r="E122" s="1">
         <v>1.09487519747564</v>
       </c>
-      <c r="J122" s="27"/>
+      <c r="J122" s="28"/>
     </row>
     <row r="123">
       <c r="A123" s="1" t="s">
@@ -9589,7 +9592,7 @@
       <c r="F123" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="J123" s="27"/>
+      <c r="J123" s="28"/>
     </row>
     <row r="124">
       <c r="B124" s="1" t="s">
@@ -9604,7 +9607,7 @@
       <c r="E124" s="1">
         <v>1.0746031465</v>
       </c>
-      <c r="J124" s="27"/>
+      <c r="J124" s="28"/>
     </row>
     <row r="125">
       <c r="A125" s="1" t="s">
@@ -9622,7 +9625,7 @@
       <c r="E125" s="1">
         <v>0.767427665351752</v>
       </c>
-      <c r="J125" s="27"/>
+      <c r="J125" s="28"/>
     </row>
     <row r="126">
       <c r="B126" s="1" t="s">
@@ -9637,7 +9640,7 @@
       <c r="E126" s="1">
         <v>1.14565358823941</v>
       </c>
-      <c r="J126" s="27"/>
+      <c r="J126" s="28"/>
     </row>
     <row r="127">
       <c r="A127" s="1" t="s">
@@ -9655,7 +9658,7 @@
       <c r="E127" s="1">
         <v>0.8090669306</v>
       </c>
-      <c r="J127" s="27"/>
+      <c r="J127" s="28"/>
     </row>
     <row r="128">
       <c r="B128" s="1" t="s">
@@ -9670,7 +9673,7 @@
       <c r="E128" s="1">
         <v>0.9732260447</v>
       </c>
-      <c r="J128" s="27"/>
+      <c r="J128" s="28"/>
     </row>
     <row r="129">
       <c r="A129" s="1" t="s">
@@ -9688,7 +9691,7 @@
       <c r="E129" s="1">
         <v>0.834754076</v>
       </c>
-      <c r="J129" s="27"/>
+      <c r="J129" s="28"/>
     </row>
     <row r="130">
       <c r="B130" s="1" t="s">
@@ -9703,7 +9706,7 @@
       <c r="E130" s="1">
         <v>0.9683953042</v>
       </c>
-      <c r="J130" s="27"/>
+      <c r="J130" s="28"/>
     </row>
     <row r="131">
       <c r="A131" s="1" t="s">
@@ -9721,7 +9724,7 @@
       <c r="E131" s="1">
         <v>0.7852399325</v>
       </c>
-      <c r="J131" s="27"/>
+      <c r="J131" s="28"/>
     </row>
     <row r="132">
       <c r="B132" s="1" t="s">
@@ -9736,7 +9739,7 @@
       <c r="E132" s="1">
         <v>0.956274921</v>
       </c>
-      <c r="J132" s="27"/>
+      <c r="J132" s="28"/>
     </row>
     <row r="133">
       <c r="A133" s="1" t="s">
@@ -9754,7 +9757,7 @@
       <c r="E133" s="1">
         <v>0.778745713440709</v>
       </c>
-      <c r="J133" s="27"/>
+      <c r="J133" s="28"/>
     </row>
     <row r="134">
       <c r="B134" s="1" t="s">
@@ -9769,7 +9772,7 @@
       <c r="E134" s="1">
         <v>1.08833633722298</v>
       </c>
-      <c r="J134" s="27"/>
+      <c r="J134" s="28"/>
     </row>
     <row r="135">
       <c r="A135" s="1" t="s">
@@ -9787,7 +9790,7 @@
       <c r="E135" s="1">
         <v>0.7791491994</v>
       </c>
-      <c r="J135" s="27"/>
+      <c r="J135" s="28"/>
     </row>
     <row r="136">
       <c r="B136" s="1" t="s">
@@ -9802,7 +9805,7 @@
       <c r="E136" s="1">
         <v>1.0405958084</v>
       </c>
-      <c r="J136" s="27"/>
+      <c r="J136" s="28"/>
     </row>
     <row r="137">
       <c r="A137" s="1" t="s">
@@ -9820,7 +9823,7 @@
       <c r="E137" s="1">
         <v>0.728108161</v>
       </c>
-      <c r="J137" s="27"/>
+      <c r="J137" s="28"/>
     </row>
     <row r="138">
       <c r="B138" s="1" t="s">
@@ -9835,7 +9838,7 @@
       <c r="E138" s="1">
         <v>1.1061910473</v>
       </c>
-      <c r="J138" s="27"/>
+      <c r="J138" s="28"/>
     </row>
     <row r="139">
       <c r="A139" s="1" t="s">
@@ -9853,7 +9856,7 @@
       <c r="E139" s="1">
         <v>0.7360634351</v>
       </c>
-      <c r="J139" s="27"/>
+      <c r="J139" s="28"/>
     </row>
     <row r="140">
       <c r="B140" s="1" t="s">
@@ -9868,7 +9871,7 @@
       <c r="E140" s="1">
         <v>0.9018015842</v>
       </c>
-      <c r="J140" s="27"/>
+      <c r="J140" s="28"/>
     </row>
     <row r="141">
       <c r="A141" s="1" t="s">
@@ -9886,7 +9889,7 @@
       <c r="E141" s="1">
         <v>0.7616601807</v>
       </c>
-      <c r="J141" s="27"/>
+      <c r="J141" s="28"/>
     </row>
     <row r="142">
       <c r="B142" s="1" t="s">
@@ -9901,7 +9904,7 @@
       <c r="E142" s="1">
         <v>1.110426904</v>
       </c>
-      <c r="J142" s="27"/>
+      <c r="J142" s="28"/>
     </row>
     <row r="143">
       <c r="A143" s="1" t="s">
@@ -9919,7 +9922,7 @@
       <c r="E143" s="1">
         <v>0.746394721629512</v>
       </c>
-      <c r="J143" s="27"/>
+      <c r="J143" s="28"/>
     </row>
     <row r="144">
       <c r="B144" s="1" t="s">
@@ -9934,7 +9937,7 @@
       <c r="E144" s="1">
         <v>1.0645070887192</v>
       </c>
-      <c r="J144" s="27"/>
+      <c r="J144" s="28"/>
     </row>
     <row r="145">
       <c r="A145" s="1" t="s">
@@ -9955,7 +9958,7 @@
       <c r="F145" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="J145" s="27"/>
+      <c r="J145" s="28"/>
     </row>
     <row r="146">
       <c r="B146" s="1" t="s">
@@ -9970,7 +9973,7 @@
       <c r="E146" s="1">
         <v>1.8035336372</v>
       </c>
-      <c r="J146" s="27"/>
+      <c r="J146" s="28"/>
     </row>
     <row r="147">
       <c r="A147" s="1" t="s">
@@ -9988,7 +9991,7 @@
       <c r="E147" s="1">
         <v>0.7706837071</v>
       </c>
-      <c r="J147" s="27"/>
+      <c r="J147" s="28"/>
     </row>
     <row r="148">
       <c r="B148" s="1" t="s">
@@ -10003,7 +10006,7 @@
       <c r="E148" s="1">
         <v>1.4951655779</v>
       </c>
-      <c r="J148" s="27"/>
+      <c r="J148" s="28"/>
     </row>
     <row r="149">
       <c r="A149" s="1" t="s">
@@ -10021,7 +10024,7 @@
       <c r="E149" s="1">
         <v>0.7332467526</v>
       </c>
-      <c r="J149" s="27"/>
+      <c r="J149" s="28"/>
     </row>
     <row r="150">
       <c r="B150" s="1" t="s">
@@ -10036,7 +10039,7 @@
       <c r="E150" s="1">
         <v>1.1810047602</v>
       </c>
-      <c r="J150" s="27"/>
+      <c r="J150" s="28"/>
     </row>
     <row r="151">
       <c r="A151" s="1" t="s">
@@ -10054,7 +10057,7 @@
       <c r="E151" s="1">
         <v>0.731822272290115</v>
       </c>
-      <c r="J151" s="27"/>
+      <c r="J151" s="28"/>
     </row>
     <row r="152">
       <c r="B152" s="1" t="s">
@@ -10069,31 +10072,31 @@
       <c r="E152" s="1">
         <v>0.85893421798748</v>
       </c>
-      <c r="J152" s="27"/>
+      <c r="J152" s="28"/>
     </row>
     <row r="153">
-      <c r="J153" s="27"/>
+      <c r="J153" s="28"/>
     </row>
     <row r="154">
-      <c r="J154" s="27"/>
+      <c r="J154" s="28"/>
     </row>
     <row r="155">
-      <c r="J155" s="27"/>
+      <c r="J155" s="28"/>
     </row>
     <row r="156">
-      <c r="J156" s="27"/>
+      <c r="J156" s="28"/>
     </row>
     <row r="157">
-      <c r="J157" s="27"/>
+      <c r="J157" s="28"/>
     </row>
     <row r="158">
-      <c r="J158" s="27"/>
+      <c r="J158" s="28"/>
     </row>
     <row r="159">
-      <c r="J159" s="27"/>
+      <c r="J159" s="28"/>
     </row>
     <row r="160">
-      <c r="J160" s="27"/>
+      <c r="J160" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/data/Mu&OffsetData.xlsx
+++ b/data/Mu&OffsetData.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="846" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="342">
   <si>
     <t>Assam Track 1</t>
   </si>
@@ -190,442 +190,502 @@
     <t>PYTHON SCRIPT</t>
   </si>
   <si>
+    <t>import numpy as np</t>
+  </si>
+  <si>
+    <t>Tile MAE: 0.0447335035339286</t>
+  </si>
+  <si>
+    <t>from sympy import true</t>
+  </si>
+  <si>
+    <t>Tile MRE %: 6.483116454192552</t>
+  </si>
+  <si>
+    <t>Cardboard MAE: 0.11570750259821426</t>
+  </si>
+  <si>
     <t>tile = (</t>
   </si>
   <si>
-    <t>Tile MAE: 0.045671434703571455</t>
-  </si>
-  <si>
-    <t>0.69180242,</t>
-  </si>
-  <si>
-    <t>Tile MRE %: 6.619048507763979</t>
-  </si>
-  <si>
-    <t>0.69359566,</t>
-  </si>
-  <si>
-    <t>Cardboard MAE: 0.12099004850535715</t>
-  </si>
-  <si>
-    <t>0.66521889,</t>
-  </si>
-  <si>
-    <t>Cardboard MRE %: 11.746606651005546</t>
+    <t>Cardboard MRE %: 11.233738116331482</t>
+  </si>
+  <si>
+    <t>0.6960932134,</t>
+  </si>
+  <si>
+    <t>Acrylic MAE: 0.13902088668333334</t>
+  </si>
+  <si>
+    <t>0.711716796,</t>
+  </si>
+  <si>
+    <t>Acrylic MRE %: 16.55010555753968</t>
+  </si>
+  <si>
+    <t>0.7205852602,</t>
+  </si>
+  <si>
+    <t>DETECTION SCORES</t>
+  </si>
+  <si>
+    <t>Tile Mean: 0.7142094662125</t>
+  </si>
+  <si>
+    <t>0.7014588838,</t>
+  </si>
+  <si>
+    <t>Precision</t>
+  </si>
+  <si>
+    <t>Cardboard Mean: 1.0385003865803573</t>
+  </si>
+  <si>
+    <t>0.7630843658,</t>
+  </si>
+  <si>
+    <t>Acrylic Mean: 0.8612170821166666</t>
+  </si>
+  <si>
+    <t>0.65954879,</t>
+  </si>
+  <si>
+    <t>0.6950948899,</t>
+  </si>
+  <si>
+    <t>0.6912420848,</t>
+  </si>
+  <si>
+    <t>Recall</t>
+  </si>
+  <si>
+    <t>0.7504805015,</t>
+  </si>
+  <si>
+    <t>0.6795514235,</t>
+  </si>
+  <si>
+    <t>0.7371280318,</t>
+  </si>
+  <si>
+    <t>0.6586842966,</t>
+  </si>
+  <si>
+    <t>F1 Score</t>
+  </si>
+  <si>
+    <t>0.7251524385,</t>
+  </si>
+  <si>
+    <t>0.6678314216,</t>
+  </si>
+  <si>
+    <t>0.6395216272,</t>
+  </si>
+  <si>
+    <t>0.630516063,</t>
+  </si>
+  <si>
+    <t>0.5967960455,</t>
+  </si>
+  <si>
+    <t>0.6952665292,</t>
+  </si>
+  <si>
+    <t>0.6998873186,</t>
+  </si>
+  <si>
+    <t>OFFSET SCORES</t>
+  </si>
+  <si>
+    <t>0.6997863982,</t>
+  </si>
+  <si>
+    <t>0.39616051 +- 0.5277770224</t>
+  </si>
+  <si>
+    <t>0.6918024201,</t>
+  </si>
+  <si>
+    <t>0.4516538837 +- 0.488965196</t>
+  </si>
+  <si>
+    <t>0.6935956635,</t>
+  </si>
+  <si>
+    <t>0.5285442784 +- 0.6097834491</t>
+  </si>
+  <si>
+    <t>0.6652188953,</t>
   </si>
   <si>
     <t>0.6785552684,</t>
   </si>
   <si>
-    <t>Acrylic MAE: 0.14036385124166664</t>
-  </si>
-  <si>
     <t>0.7404798108,</t>
   </si>
   <si>
-    <t>Acrylic MRE %: 16.709982290674603</t>
-  </si>
-  <si>
-    <t>0.7223886906,</t>
-  </si>
-  <si>
-    <t>DETECTION SCORES</t>
-  </si>
-  <si>
-    <t>Tile Mean: 0.7157199866321429</t>
-  </si>
-  <si>
-    <t>0.693855759,</t>
-  </si>
-  <si>
-    <t>Precision</t>
-  </si>
-  <si>
-    <t>Cardboard Mean: 1.0332178404232144</t>
+    <t>0.7223886907,</t>
+  </si>
+  <si>
+    <t>0.6938557598,</t>
   </si>
   <si>
     <t>0.6759991876,</t>
   </si>
   <si>
-    <t>Acrylic Mean: 0.8670846764416666</t>
-  </si>
-  <si>
     <t>0.6175559023,</t>
   </si>
   <si>
-    <t>0.648114875,</t>
+    <t>0.6481148752,</t>
   </si>
   <si>
     <t>0.6756369776,</t>
   </si>
   <si>
-    <t>Recall</t>
-  </si>
-  <si>
-    <t>0.7324887418,</t>
+    <t>0.7324887419,</t>
+  </si>
+  <si>
+    <t>0.6739674954,</t>
+  </si>
+  <si>
+    <t>0.6695189558,</t>
+  </si>
+  <si>
+    <t>0.7058638883,</t>
+  </si>
+  <si>
+    <t>0.6993529493,</t>
+  </si>
+  <si>
+    <t>0.7631135756,</t>
+  </si>
+  <si>
+    <t>0.7634124267,</t>
+  </si>
+  <si>
+    <t>0.8149010226,</t>
+  </si>
+  <si>
+    <t>0.7402349295,</t>
+  </si>
+  <si>
+    <t>0.7606694346,</t>
+  </si>
+  <si>
+    <t>0.62830973,</t>
+  </si>
+  <si>
+    <t>0.7674276654,</t>
+  </si>
+  <si>
+    <t>0.8090669306,</t>
+  </si>
+  <si>
+    <t>0.834754076,</t>
+  </si>
+  <si>
+    <t>0.7852399325,</t>
+  </si>
+  <si>
+    <t>0.7787457134,</t>
+  </si>
+  <si>
+    <t>0.7791491994,</t>
+  </si>
+  <si>
+    <t>0.728108161,</t>
+  </si>
+  <si>
+    <t>0.7360634351,</t>
+  </si>
+  <si>
+    <t>0.7616601807,</t>
+  </si>
+  <si>
+    <t>0.7463947216,</t>
+  </si>
+  <si>
+    <t>0.7589043801,</t>
+  </si>
+  <si>
+    <t>0.7706837071,</t>
+  </si>
+  <si>
+    <t>0.7332467526,</t>
+  </si>
+  <si>
+    <t>)</t>
+  </si>
+  <si>
+    <t>cardboard = (</t>
+  </si>
+  <si>
+    <t>0.8415899703,</t>
+  </si>
+  <si>
+    <t>1.125711839,</t>
+  </si>
+  <si>
+    <t>1.17147256,</t>
+  </si>
+  <si>
+    <t>0.9486374599,</t>
+  </si>
+  <si>
+    <t>1.093933765,</t>
+  </si>
+  <si>
+    <t>1.223298434,</t>
+  </si>
+  <si>
+    <t>1.238564351,</t>
+  </si>
+  <si>
+    <t>1.207087062,</t>
+  </si>
+  <si>
+    <t>1.127376863,</t>
+  </si>
+  <si>
+    <t>0.928818455,</t>
+  </si>
+  <si>
+    <t>1.065439565,</t>
+  </si>
+  <si>
+    <t>1.084426998,</t>
+  </si>
+  <si>
+    <t>1.002671496,</t>
+  </si>
+  <si>
+    <t>0.9468346919,</t>
+  </si>
+  <si>
+    <t>1.048652702,</t>
+  </si>
+  <si>
+    <t>0.9765088555,</t>
+  </si>
+  <si>
+    <t>0.8813267071,</t>
+  </si>
+  <si>
+    <t>0.9142219725,</t>
+  </si>
+  <si>
+    <t>0.936962369,</t>
+  </si>
+  <si>
+    <t>1.02945182,</t>
+  </si>
+  <si>
+    <t>0.9907632305,</t>
+  </si>
+  <si>
+    <t>1.057365017,</t>
+  </si>
+  <si>
+    <t>0.9292311212,</t>
+  </si>
+  <si>
+    <t>0.8446965494,</t>
+  </si>
+  <si>
+    <t>1.041958062,</t>
+  </si>
+  <si>
+    <t>0.8750385896,</t>
+  </si>
+  <si>
+    <t>0.8980291949,</t>
+  </si>
+  <si>
+    <t>1.059625954,</t>
+  </si>
+  <si>
+    <t>1.055265147,</t>
+  </si>
+  <si>
+    <t>0.8983166196,</t>
+  </si>
+  <si>
+    <t>1.095908065,</t>
+  </si>
+  <si>
+    <t>1.032604116,</t>
+  </si>
+  <si>
+    <t>0.9697900619,</t>
+  </si>
+  <si>
+    <t>0.8664588519,</t>
+  </si>
+  <si>
+    <t>1.04363914,</t>
+  </si>
+  <si>
+    <t>0.8183505199,</t>
+  </si>
+  <si>
+    <t>0.7938452464,</t>
+  </si>
+  <si>
+    <t>0.8280248969,</t>
+  </si>
+  <si>
+    <t>1.1734409,</t>
+  </si>
+  <si>
+    <t>1.227157265,</t>
+  </si>
+  <si>
+    <t>1.094875197,</t>
+  </si>
+  <si>
+    <t>1.074603147,</t>
+  </si>
+  <si>
+    <t>1.145653588,</t>
+  </si>
+  <si>
+    <t>0.9732260447,</t>
+  </si>
+  <si>
+    <t>0.9683953042,</t>
+  </si>
+  <si>
+    <t>0.956274921,</t>
+  </si>
+  <si>
+    <t>1.088336337,</t>
+  </si>
+  <si>
+    <t>1.040595808,</t>
+  </si>
+  <si>
+    <t>1.106191047,</t>
+  </si>
+  <si>
+    <t>0.9018015842,</t>
+  </si>
+  <si>
+    <t>1.110426904,</t>
+  </si>
+  <si>
+    <t>1.064507089,</t>
+  </si>
+  <si>
+    <t>1.803533637,</t>
+  </si>
+  <si>
+    <t>1.495165578,</t>
+  </si>
+  <si>
+    <t>1.18100476,</t>
+  </si>
+  <si>
+    <t>acrylic = (</t>
+  </si>
+  <si>
+    <t>0.9127304548,</t>
+  </si>
+  <si>
+    <t>0.9801569032,</t>
+  </si>
+  <si>
+    <t>0.8675244117,</t>
+  </si>
+  <si>
+    <t>1.074897362,</t>
+  </si>
+  <si>
+    <t>0.9176910204,</t>
+  </si>
+  <si>
+    <t>0.7205485175,</t>
+  </si>
+  <si>
+    <t>0.9599639196,</t>
+  </si>
+  <si>
+    <t>0.9006794133,</t>
+  </si>
+  <si>
+    <t>1.105868102,</t>
+  </si>
+  <si>
+    <t>0.6981543221,</t>
+  </si>
+  <si>
+    <t>0.7520148837,</t>
+  </si>
+  <si>
+    <t>0.9668405456,</t>
+  </si>
+  <si>
+    <t>0.7233920819,</t>
+  </si>
+  <si>
+    <t>1.043626269,</t>
+  </si>
+  <si>
+    <t>0.7675737622,</t>
+  </si>
+  <si>
+    <t>0.6747166092,</t>
+  </si>
+  <si>
+    <t>0.6826693048,</t>
+  </si>
+  <si>
+    <t>0.722906372,</t>
+  </si>
+  <si>
+    <t>1.061705111,</t>
+  </si>
+  <si>
+    <t>0.9164378401,</t>
+  </si>
+  <si>
+    <t>0.82483737,</t>
+  </si>
+  <si>
+    <t>0.9511330905,</t>
+  </si>
+  <si>
+    <t>0.9478648152,</t>
+  </si>
+  <si>
+    <t>0.7181710076,</t>
+  </si>
+  <si>
+    <t>0.6789101833,</t>
+  </si>
+  <si>
+    <t>1.390464671,</t>
+  </si>
+  <si>
+    <t>0.7200478942,</t>
+  </si>
+  <si>
+    <t>0.7635727213,</t>
+  </si>
+  <si>
+    <t>0.7068303252,</t>
+  </si>
+  <si>
+    <t>0.7293578089,</t>
+  </si>
+  <si>
+    <t>0.774511134,</t>
   </si>
   <si>
     <t>0.7585566574,</t>
   </si>
   <si>
-    <t>0.6695189557,</t>
-  </si>
-  <si>
-    <t>0.70586388,</t>
-  </si>
-  <si>
-    <t>F1 Score</t>
-  </si>
-  <si>
-    <t>0.6993529493,</t>
-  </si>
-  <si>
-    <t>0.6960932134,</t>
-  </si>
-  <si>
-    <t>0.711716796,</t>
-  </si>
-  <si>
-    <t>0.7205852602,</t>
-  </si>
-  <si>
-    <t>0.7014588838,</t>
-  </si>
-  <si>
-    <t>0.7630843658,</t>
-  </si>
-  <si>
-    <t>0.65954879,</t>
-  </si>
-  <si>
-    <t>OFFSET SCORES</t>
-  </si>
-  <si>
-    <t>0.6950948899,</t>
-  </si>
-  <si>
-    <t>0.39616051 +- 0.5277770224</t>
-  </si>
-  <si>
-    <t>0.6912420848,</t>
-  </si>
-  <si>
-    <t>0.4516538837 +- 0.488965196</t>
-  </si>
-  <si>
-    <t>0.7504805015,</t>
-  </si>
-  <si>
-    <t>0.5285442784 +- 0.6097834491</t>
-  </si>
-  <si>
-    <t>0.6795514235,</t>
-  </si>
-  <si>
-    <t>0.7371280318,</t>
-  </si>
-  <si>
-    <t>0.6586842966,</t>
-  </si>
-  <si>
-    <t>0.7251524385,</t>
-  </si>
-  <si>
-    <t>0.6678314216,</t>
-  </si>
-  <si>
-    <t>0.6395216272,</t>
-  </si>
-  <si>
-    <t>0.630516063,</t>
-  </si>
-  <si>
-    <t>0.5967960455,</t>
-  </si>
-  <si>
-    <t>0.6952665292,</t>
-  </si>
-  <si>
-    <t>0.6998873186,</t>
-  </si>
-  <si>
-    <t>0.6997863982,</t>
-  </si>
-  <si>
-    <t>0.7631135756,</t>
-  </si>
-  <si>
-    <t>0.7634124267,</t>
-  </si>
-  <si>
-    <t>0.8149010226,</t>
-  </si>
-  <si>
-    <t>0.7402349295,</t>
-  </si>
-  <si>
-    <t>0.7606694346,</t>
-  </si>
-  <si>
-    <t>0.62830973,</t>
-  </si>
-  <si>
-    <t>0.7674276654,</t>
-  </si>
-  <si>
-    <t>0.8090669306,</t>
-  </si>
-  <si>
-    <t>0.834754076,</t>
-  </si>
-  <si>
-    <t>0.7852399325,</t>
-  </si>
-  <si>
-    <t>0.7787457134,</t>
-  </si>
-  <si>
-    <t>0.7791491994,</t>
-  </si>
-  <si>
-    <t>0.728108161,</t>
-  </si>
-  <si>
-    <t>0.7360634351,</t>
-  </si>
-  <si>
-    <t>0.7616601807,</t>
-  </si>
-  <si>
-    <t>0.7463947216,</t>
-  </si>
-  <si>
-    <t>0.7589043801,</t>
-  </si>
-  <si>
-    <t>0.7706837071,</t>
-  </si>
-  <si>
-    <t>0.7332467526,</t>
-  </si>
-  <si>
-    <t>0.7318222723,</t>
-  </si>
-  <si>
-    <t>)</t>
-  </si>
-  <si>
-    <t>cardboard = (</t>
-  </si>
-  <si>
-    <t>0.99076323,</t>
-  </si>
-  <si>
-    <t>1.057365016,</t>
-  </si>
-  <si>
-    <t>0.92923112,</t>
-  </si>
-  <si>
-    <t>0.8446965494,</t>
-  </si>
-  <si>
-    <t>1.041958061,</t>
-  </si>
-  <si>
-    <t>0.87503858,</t>
-  </si>
-  <si>
-    <t>0.8980291949,</t>
-  </si>
-  <si>
-    <t>1.05962595,</t>
-  </si>
-  <si>
-    <t>1.055265147,</t>
-  </si>
-  <si>
-    <t>0.8983166196,</t>
-  </si>
-  <si>
-    <t>1.095908064,</t>
-  </si>
-  <si>
-    <t>1.032604115,</t>
-  </si>
-  <si>
-    <t>0.6739674954,</t>
-  </si>
-  <si>
-    <t>0.8664588519,</t>
-  </si>
-  <si>
-    <t>1.04363914,</t>
-  </si>
-  <si>
-    <t>0.8183505199,</t>
-  </si>
-  <si>
-    <t>0.8415899703,</t>
-  </si>
-  <si>
-    <t>1.125711839,</t>
-  </si>
-  <si>
-    <t>1.17147256,</t>
-  </si>
-  <si>
-    <t>0.9486374599,</t>
-  </si>
-  <si>
-    <t>1.093933765,</t>
-  </si>
-  <si>
-    <t>1.223298434,</t>
-  </si>
-  <si>
-    <t>1.238564351,</t>
-  </si>
-  <si>
-    <t>1.207087062,</t>
-  </si>
-  <si>
-    <t>1.127376863,</t>
-  </si>
-  <si>
-    <t>0.928818455,</t>
-  </si>
-  <si>
-    <t>1.065439565,</t>
-  </si>
-  <si>
-    <t>1.084426998,</t>
-  </si>
-  <si>
-    <t>1.002671496,</t>
-  </si>
-  <si>
-    <t>0.9468346919,</t>
-  </si>
-  <si>
-    <t>1.048652702,</t>
-  </si>
-  <si>
-    <t>0.9765088555,</t>
-  </si>
-  <si>
-    <t>0.8813267071,</t>
-  </si>
-  <si>
-    <t>0.9142219725,</t>
-  </si>
-  <si>
-    <t>0.936962369,</t>
-  </si>
-  <si>
-    <t>1.02945182,</t>
-  </si>
-  <si>
-    <t>0.7938452464,</t>
-  </si>
-  <si>
-    <t>0.8280248969,</t>
-  </si>
-  <si>
-    <t>1.1734409,</t>
-  </si>
-  <si>
-    <t>1.227157265,</t>
-  </si>
-  <si>
-    <t>1.094875198,</t>
-  </si>
-  <si>
-    <t>1.074603147,</t>
-  </si>
-  <si>
-    <t>1.145653588,</t>
-  </si>
-  <si>
-    <t>0.9732260447,</t>
-  </si>
-  <si>
-    <t>0.9683953042,</t>
-  </si>
-  <si>
-    <t>0.956274921,</t>
-  </si>
-  <si>
-    <t>1.088336337,</t>
-  </si>
-  <si>
-    <t>1.040595808,</t>
-  </si>
-  <si>
-    <t>1.106191047,</t>
-  </si>
-  <si>
-    <t>0.9018015842,</t>
-  </si>
-  <si>
-    <t>1.110426904,</t>
-  </si>
-  <si>
-    <t>1.064507089,</t>
-  </si>
-  <si>
-    <t>1.803533637,</t>
-  </si>
-  <si>
-    <t>1.495165578,</t>
-  </si>
-  <si>
-    <t>1.18100476,</t>
-  </si>
-  <si>
-    <t>0.858934218,</t>
-  </si>
-  <si>
-    <t>acrylic = (</t>
-  </si>
-  <si>
-    <t>0.82483737,</t>
-  </si>
-  <si>
-    <t>0.9511330905,</t>
-  </si>
-  <si>
-    <t>0.9478648151,</t>
-  </si>
-  <si>
-    <t>0.7181710075,</t>
-  </si>
-  <si>
-    <t>0.6789101833,</t>
-  </si>
-  <si>
-    <t>1.390464671,</t>
-  </si>
-  <si>
-    <t>0.72004789,</t>
-  </si>
-  <si>
-    <t>0.76357272,</t>
-  </si>
-  <si>
-    <t>0.706830325,</t>
-  </si>
-  <si>
-    <t>0.729357808,</t>
-  </si>
-  <si>
-    <t>0.7745111339,</t>
-  </si>
-  <si>
-    <t>0.969790061,</t>
-  </si>
-  <si>
-    <t>1.128843535,</t>
+    <t>1.128843536,</t>
   </si>
   <si>
     <t>1.037855973,</t>
@@ -634,69 +694,6 @@
     <t>0.7070192763,</t>
   </si>
   <si>
-    <t>0.7157412862,</t>
-  </si>
-  <si>
-    <t>0.9127304548,</t>
-  </si>
-  <si>
-    <t>0.9801569032,</t>
-  </si>
-  <si>
-    <t>0.8675244117,</t>
-  </si>
-  <si>
-    <t>1.074897362,</t>
-  </si>
-  <si>
-    <t>0.9176910204,</t>
-  </si>
-  <si>
-    <t>0.7205485175,</t>
-  </si>
-  <si>
-    <t>0.9599639196,</t>
-  </si>
-  <si>
-    <t>0.9006794133,</t>
-  </si>
-  <si>
-    <t>1.105868102,</t>
-  </si>
-  <si>
-    <t>0.6981543221,</t>
-  </si>
-  <si>
-    <t>0.7520148837,</t>
-  </si>
-  <si>
-    <t>0.9668405456,</t>
-  </si>
-  <si>
-    <t>0.7233920819,</t>
-  </si>
-  <si>
-    <t>1.043626269,</t>
-  </si>
-  <si>
-    <t>0.7675737622,</t>
-  </si>
-  <si>
-    <t>0.6747166092,</t>
-  </si>
-  <si>
-    <t>0.6826693048,</t>
-  </si>
-  <si>
-    <t>0.722906372,</t>
-  </si>
-  <si>
-    <t>1.061705111,</t>
-  </si>
-  <si>
-    <t>0.9164378401,</t>
-  </si>
-  <si>
     <t>true_tile_mu = 0.69</t>
   </si>
   <si>
@@ -706,9 +703,6 @@
     <t>true_acrylic_mu = 0.84</t>
   </si>
   <si>
-    <t>import numpy as np</t>
-  </si>
-  <si>
     <t>def mae(pred, true):</t>
   </si>
   <si>
@@ -718,7 +712,7 @@
     <t>def mre(pred, true):</t>
   </si>
   <si>
-    <t>return np.mean(np.abs(pred - true) / abs(true))</t>
+    <t>return np.mean(np.abs(pred - true) / np.abs(true))</t>
   </si>
   <si>
     <t>tile = np.array(tile)</t>
@@ -764,6 +758,15 @@
   </si>
   <si>
     <t>print("Acrylic MRE %:", acrylic_mre * 100)</t>
+  </si>
+  <si>
+    <t>print("Tile Mean:", np.mean(tile))</t>
+  </si>
+  <si>
+    <t>print("Cardboard Mean:", np.mean(cardboard))</t>
+  </si>
+  <si>
+    <t>print("Acrylic Mean:", np.mean(acrylic))</t>
   </si>
   <si>
     <t>Mu Value From Folds</t>
@@ -1330,7 +1333,7 @@
     <xf borderId="12" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="12" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="13" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
@@ -4360,70 +4363,68 @@
       <c r="C3" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>57</v>
-      </c>
+      <c r="I3" s="1"/>
     </row>
     <row r="4">
       <c r="C4" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="I4" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="5">
       <c r="C5" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="I5" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="6">
       <c r="C6" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="I6" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="7">
       <c r="C7" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="I7" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="I8" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="C9" s="20" t="s">
+      <c r="I9" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="10">
       <c r="C10" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="I10" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="11">
@@ -4431,25 +4432,25 @@
         <v>0.961</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12">
       <c r="I12" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="I13" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="14">
       <c r="I14" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15">
@@ -4457,25 +4458,25 @@
         <v>1.0</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16">
       <c r="I16" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="I17" s="1" t="s">
         <v>81</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="18">
       <c r="I18" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="19">
@@ -4483,35 +4484,35 @@
         <v>0.9801</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="20">
       <c r="I20" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21">
       <c r="I21" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="22">
       <c r="I22" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="23">
       <c r="I23" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="I24" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="25">
@@ -4519,10 +4520,10 @@
         <v>17</v>
       </c>
       <c r="B25" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="I25" s="1" t="s">
         <v>91</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="26">
@@ -4530,10 +4531,10 @@
         <v>14</v>
       </c>
       <c r="B26" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="I26" s="1" t="s">
         <v>93</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="27">
@@ -4541,760 +4542,811 @@
         <v>15</v>
       </c>
       <c r="B27" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="I27" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="28">
       <c r="I28" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="29">
       <c r="I29" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="30">
       <c r="I30" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="31">
       <c r="I31" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="32">
       <c r="I32" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33">
       <c r="I33" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="34">
       <c r="I34" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="35">
       <c r="I35" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="36">
       <c r="I36" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="37">
       <c r="I37" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="38">
       <c r="I38" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="39">
       <c r="I39" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="40">
       <c r="I40" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="41">
       <c r="I41" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="42">
       <c r="I42" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="43">
       <c r="I43" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="44">
       <c r="I44" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="45">
       <c r="I45" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="46">
       <c r="I46" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="47">
       <c r="I47" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="48">
       <c r="I48" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="49">
       <c r="I49" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="50">
       <c r="I50" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="51">
       <c r="I51" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="52">
       <c r="I52" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="53">
       <c r="I53" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="54">
       <c r="I54" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="55">
       <c r="I55" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="56">
       <c r="I56" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="57">
       <c r="I57" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="58">
       <c r="I58" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="I59" s="1" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="60">
-      <c r="I60" s="1" t="s">
-        <v>128</v>
+      <c r="I60" s="1">
+        <v>0.7318222723</v>
       </c>
     </row>
     <row r="61">
       <c r="I61" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="62">
-      <c r="I62" s="1" t="s">
-        <v>130</v>
-      </c>
+      <c r="I62" s="1"/>
     </row>
     <row r="63">
       <c r="I63" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="64">
       <c r="I64" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="65">
       <c r="I65" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="66">
       <c r="I66" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="67">
       <c r="I67" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="68">
       <c r="I68" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="69">
       <c r="I69" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="70">
       <c r="I70" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="71">
       <c r="I71" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="72">
       <c r="I72" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="73">
       <c r="I73" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="74">
       <c r="I74" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="75">
       <c r="I75" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="76">
       <c r="I76" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="77">
       <c r="I77" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="78">
       <c r="I78" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="79">
       <c r="I79" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="80">
       <c r="I80" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="81">
       <c r="I81" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="82">
       <c r="I82" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="83">
       <c r="I83" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="84">
       <c r="I84" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="85">
       <c r="I85" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="86">
       <c r="I86" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="87">
       <c r="I87" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="88">
       <c r="I88" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="89">
       <c r="I89" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="90">
       <c r="I90" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="91">
       <c r="I91" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="92">
       <c r="I92" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="93">
       <c r="I93" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="94">
       <c r="I94" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="95">
       <c r="I95" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="96">
       <c r="I96" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="97">
       <c r="I97" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="98">
       <c r="I98" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="99">
       <c r="I99" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="100">
       <c r="I100" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="101">
       <c r="I101" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="102">
       <c r="I102" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="103">
       <c r="I103" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="104">
       <c r="I104" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="105">
       <c r="I105" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="106">
       <c r="I106" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="107">
       <c r="I107" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="108">
       <c r="I108" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="109">
       <c r="I109" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="110">
       <c r="I110" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="111">
       <c r="I111" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="112">
       <c r="I112" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="113">
       <c r="I113" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="114">
       <c r="I114" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="115">
       <c r="I115" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="116">
       <c r="I116" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="117">
       <c r="I117" s="1" t="s">
-        <v>127</v>
+        <v>183</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="I118" s="1" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="119">
-      <c r="I119" s="1" t="s">
-        <v>185</v>
+      <c r="I119" s="1">
+        <v>0.858934218</v>
       </c>
     </row>
     <row r="120">
       <c r="I120" s="1" t="s">
-        <v>186</v>
+        <v>128</v>
       </c>
     </row>
     <row r="121">
-      <c r="I121" s="1" t="s">
-        <v>187</v>
-      </c>
+      <c r="I121" s="1"/>
     </row>
     <row r="122">
       <c r="I122" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="123">
       <c r="I123" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="124">
       <c r="I124" s="1" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="125">
       <c r="I125" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="126">
       <c r="I126" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="127">
       <c r="I127" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="128">
       <c r="I128" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="129">
       <c r="I129" s="1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="130">
       <c r="I130" s="1" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="131">
       <c r="I131" s="1" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="132">
       <c r="I132" s="1" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="133">
       <c r="I133" s="1" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="134">
       <c r="I134" s="1" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="135">
       <c r="I135" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="136">
       <c r="I136" s="1" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="137">
       <c r="I137" s="1" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="138">
       <c r="I138" s="1" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="139">
       <c r="I139" s="1" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="140">
       <c r="I140" s="1" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="141">
       <c r="I141" s="1" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="142">
       <c r="I142" s="1" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="143">
       <c r="I143" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="144">
       <c r="I144" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="145">
       <c r="I145" s="1" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="146">
       <c r="I146" s="1" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="147">
       <c r="I147" s="1" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="148">
       <c r="I148" s="1" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="149">
       <c r="I149" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="150">
       <c r="I150" s="1" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="151">
       <c r="I151" s="1" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="152">
       <c r="I152" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="153">
       <c r="I153" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="154">
       <c r="I154" s="1" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
     <row r="155">
       <c r="I155" s="1" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="156">
       <c r="I156" s="1" t="s">
-        <v>127</v>
+        <v>219</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="I157" s="1" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="158">
-      <c r="I158" s="1" t="s">
-        <v>222</v>
+      <c r="I158" s="1">
+        <v>0.7157412862</v>
       </c>
     </row>
     <row r="159">
       <c r="I159" s="1" t="s">
-        <v>223</v>
+        <v>128</v>
       </c>
     </row>
     <row r="160">
-      <c r="I160" s="1" t="s">
-        <v>224</v>
+      <c r="I160" s="1"/>
+    </row>
+    <row r="161">
+      <c r="I161" s="1" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="162">
       <c r="I162" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="I163" s="1" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="164">
-      <c r="I164" s="1" t="s">
-        <v>226</v>
-      </c>
+      <c r="I164" s="1"/>
     </row>
     <row r="165">
       <c r="I165" s="1" t="s">
-        <v>227</v>
+        <v>53</v>
       </c>
     </row>
     <row r="167">
       <c r="I167" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="168">
       <c r="I168" s="1" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
     </row>
     <row r="170">
       <c r="I170" s="1" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
     </row>
     <row r="171">
       <c r="I171" s="1" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="172">
-      <c r="I172" s="1" t="s">
-        <v>232</v>
+      <c r="I172" s="1"/>
+    </row>
+    <row r="173">
+      <c r="I173" s="1" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="174">
       <c r="I174" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="175">
       <c r="I175" s="1" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="176">
-      <c r="I176" s="1" t="s">
-        <v>235</v>
+      <c r="I176" s="1"/>
+    </row>
+    <row r="177">
+      <c r="I177" s="1" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="178">
       <c r="I178" s="1" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
     </row>
     <row r="179">
       <c r="I179" s="1" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
     </row>
     <row r="180">
-      <c r="I180" s="1" t="s">
-        <v>238</v>
+      <c r="I180" s="1"/>
+    </row>
+    <row r="181">
+      <c r="I181" s="1" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="182">
       <c r="I182" s="1" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
     </row>
     <row r="183">
       <c r="I183" s="1" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
     <row r="185">
       <c r="I185" s="1" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="186">
       <c r="I186" s="1" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
     </row>
     <row r="188">
       <c r="I188" s="1" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
     </row>
     <row r="189">
       <c r="I189" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="I191" s="1" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="I192" s="1" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="I194" s="1" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="I195" s="1" t="s">
         <v>244</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="I196" s="1" t="s">
+        <v>245</v>
       </c>
     </row>
   </sheetData>
@@ -5353,10 +5405,10 @@
         <v>11</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="3">
@@ -6142,7 +6194,7 @@
         <v>0.648114875180265</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="31">
@@ -6686,7 +6738,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="2">
@@ -6725,7 +6777,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>17</v>
@@ -6751,7 +6803,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>17</v>
@@ -6776,7 +6828,7 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>17</v>
@@ -6788,7 +6840,7 @@
         <v>0.8149010226</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="8">
@@ -6804,7 +6856,7 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>17</v>
@@ -6831,7 +6883,7 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>17</v>
@@ -6856,7 +6908,7 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>17</v>
@@ -6868,7 +6920,7 @@
         <v>0.62830973</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="14">
@@ -6885,7 +6937,7 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>17</v>
@@ -6913,7 +6965,7 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>17</v>
@@ -6938,7 +6990,7 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>17</v>
@@ -6963,7 +7015,7 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>17</v>
@@ -6988,7 +7040,7 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>17</v>
@@ -7013,7 +7065,7 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>17</v>
@@ -7038,7 +7090,7 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>17</v>
@@ -7063,7 +7115,7 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>17</v>
@@ -7075,7 +7127,7 @@
         <v>0.7360634351</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="30">
@@ -7091,7 +7143,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>17</v>
@@ -7116,7 +7168,7 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>17</v>
@@ -7141,7 +7193,7 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>17</v>
@@ -7166,7 +7218,7 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>17</v>
@@ -7191,7 +7243,7 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>17</v>
@@ -7216,7 +7268,7 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>17</v>
@@ -7288,7 +7340,7 @@
         <v>7</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>9</v>
@@ -7297,7 +7349,7 @@
         <v>11</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
@@ -7307,7 +7359,7 @@
     </row>
     <row r="2">
       <c r="A2" s="27" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L2" s="2"/>
     </row>
@@ -7330,19 +7382,19 @@
       <c r="J3" s="28"/>
       <c r="K3" s="29"/>
       <c r="M3" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="V3" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Y3" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="4">
@@ -7350,7 +7402,7 @@
         <v>15</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D4" s="1">
         <v>1.77068523261237E9</v>
@@ -7361,19 +7413,19 @@
       <c r="J4" s="28"/>
       <c r="K4" s="29"/>
       <c r="M4" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="S4" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Y4" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="5">
@@ -7381,7 +7433,7 @@
         <v>17</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D5" s="1">
         <v>1.77068523551588E9</v>
@@ -7392,19 +7444,19 @@
       <c r="J5" s="28"/>
       <c r="K5" s="29"/>
       <c r="M5" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="S5" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="V5" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Y5" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="6">
@@ -7426,19 +7478,19 @@
       <c r="J6" s="28"/>
       <c r="K6" s="29"/>
       <c r="M6" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="S6" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="V6" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Y6" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="7">
@@ -7446,7 +7498,7 @@
         <v>15</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D7" s="1">
         <v>1.77068525799621E9</v>
@@ -7457,19 +7509,19 @@
       <c r="J7" s="28"/>
       <c r="K7" s="29"/>
       <c r="M7" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="S7" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Y7" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="8">
@@ -7477,7 +7529,7 @@
         <v>17</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D8" s="1">
         <v>1.77068526243618E9</v>
@@ -7488,19 +7540,19 @@
       <c r="J8" s="28"/>
       <c r="K8" s="29"/>
       <c r="M8" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="S8" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="V8" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Y8" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="9">
@@ -7522,19 +7574,19 @@
       <c r="J9" s="28"/>
       <c r="K9" s="29"/>
       <c r="M9" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="S9" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="V9" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Y9" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="10">
@@ -7542,7 +7594,7 @@
         <v>15</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D10" s="1">
         <v>1.77068528049645E9</v>
@@ -7553,19 +7605,19 @@
       <c r="J10" s="28"/>
       <c r="K10" s="29"/>
       <c r="M10" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="S10" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="V10" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Y10" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="11">
@@ -7573,7 +7625,7 @@
         <v>17</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D11" s="1">
         <v>1.7706852832317E9</v>
@@ -7584,19 +7636,19 @@
       <c r="J11" s="28"/>
       <c r="K11" s="29"/>
       <c r="M11" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="S11" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="V11" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="Y11" s="1" t="s">
         <v>317</v>
-      </c>
-      <c r="V11" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="Y11" s="1" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="12">
@@ -7616,24 +7668,24 @@
         <v>0.9486374599</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="J12" s="28"/>
       <c r="K12" s="29"/>
       <c r="M12" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="S12" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="V12" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Y12" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="13">
@@ -7641,7 +7693,7 @@
         <v>15</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D13" s="1">
         <v>1.77068530251681E9</v>
@@ -7652,19 +7704,19 @@
       <c r="J13" s="28"/>
       <c r="K13" s="29"/>
       <c r="M13" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="S13" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="V13" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Y13" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="14">
@@ -7672,7 +7724,7 @@
         <v>17</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D14" s="1">
         <v>1.77068530609197E9</v>
@@ -7683,19 +7735,19 @@
       <c r="J14" s="28"/>
       <c r="K14" s="29"/>
       <c r="M14" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="S14" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="V14" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Y14" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="15">
@@ -7717,19 +7769,19 @@
       <c r="J15" s="28"/>
       <c r="K15" s="29"/>
       <c r="M15" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="S15" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="V15" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="Y15" s="1" t="s">
         <v>336</v>
-      </c>
-      <c r="V15" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="Y15" s="1" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="16">
@@ -7737,7 +7789,7 @@
         <v>15</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D16" s="1">
         <v>1.77068532815744E9</v>
@@ -7753,7 +7805,7 @@
         <v>17</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D17" s="1">
         <v>1.77068533195232E9</v>
@@ -7788,7 +7840,7 @@
         <v>15</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D19" s="1">
         <v>1.77068535077796E9</v>
@@ -7804,7 +7856,7 @@
         <v>17</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D20" s="1">
         <v>1.77068535437281E9</v>
@@ -7839,7 +7891,7 @@
         <v>15</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D22" s="1">
         <v>1.77068537333746E9</v>
@@ -7861,7 +7913,7 @@
         <v>17</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D23" s="1">
         <v>1.77068537645816E9</v>
@@ -7900,7 +7952,7 @@
         <v>15</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D25" s="1">
         <v>1.77068542181798E9</v>
@@ -7916,7 +7968,7 @@
         <v>17</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D26" s="1">
         <v>1.77068542471798E9</v>
@@ -7951,7 +8003,7 @@
         <v>15</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D28" s="1">
         <v>1.77068544231808E9</v>
@@ -7967,7 +8019,7 @@
         <v>17</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D29" s="1">
         <v>1.77068544553801E9</v>
@@ -8002,7 +8054,7 @@
         <v>15</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D31" s="1">
         <v>1.77068546475331E9</v>
@@ -8018,7 +8070,7 @@
         <v>17</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D32" s="1">
         <v>1.77068546793845E9</v>
@@ -8053,7 +8105,7 @@
         <v>15</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D34" s="1">
         <v>1.77068548551845E9</v>
@@ -8069,7 +8121,7 @@
         <v>17</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D35" s="1">
         <v>1.77068548841408E9</v>
@@ -8104,7 +8156,7 @@
         <v>15</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D37" s="1">
         <v>1.7706855191939E9</v>
@@ -8120,7 +8172,7 @@
         <v>17</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D38" s="1">
         <v>1.77068552191907E9</v>
@@ -8155,7 +8207,7 @@
         <v>15</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D40" s="1">
         <v>1.77068554385939E9</v>
@@ -8171,7 +8223,7 @@
         <v>17</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D41" s="1">
         <v>1.7706855468542E9</v>
@@ -8206,7 +8258,7 @@
         <v>15</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D43" s="1">
         <v>1.77068556507437E9</v>
@@ -8222,7 +8274,7 @@
         <v>17</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D44" s="1">
         <v>1.77068556798029E9</v>
@@ -8257,7 +8309,7 @@
         <v>15</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D46" s="1">
         <v>1.77068558635768E9</v>
@@ -8273,7 +8325,7 @@
         <v>17</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D47" s="1">
         <v>1.77068558915489E9</v>
@@ -8308,7 +8360,7 @@
         <v>15</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D49" s="1">
         <v>1.77068560775506E9</v>
@@ -8324,7 +8376,7 @@
         <v>17</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D50" s="1">
         <v>1.77068561027965E9</v>
@@ -8352,7 +8404,7 @@
         <v>0.8813267071</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="J51" s="28"/>
       <c r="K51" s="29"/>
@@ -8362,7 +8414,7 @@
         <v>15</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D52" s="1">
         <v>1.77068562847506E9</v>
@@ -8378,7 +8430,7 @@
         <v>17</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D53" s="1">
         <v>1.77068563145972E9</v>
@@ -8413,7 +8465,7 @@
         <v>15</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D55" s="1">
         <v>1.77068565473496E9</v>
@@ -8429,7 +8481,7 @@
         <v>17</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D56" s="1">
         <v>1.77068565725507E9</v>
@@ -8464,7 +8516,7 @@
         <v>15</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D58" s="1">
         <v>1.77068568578035E9</v>
@@ -8480,7 +8532,7 @@
         <v>17</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D59" s="1">
         <v>1.77068568869544E9</v>
@@ -8515,7 +8567,7 @@
         <v>15</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D61" s="1">
         <v>1.77068570534603E9</v>
@@ -8532,7 +8584,7 @@
         <v>17</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D62" s="1">
         <v>1.7706857078605E9</v>
@@ -8545,10 +8597,10 @@
     </row>
     <row r="63">
       <c r="A63" s="27" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J63" s="2"/>
       <c r="K63" s="2"/>
@@ -8577,7 +8629,7 @@
         <v>14</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D65" s="1">
         <v>1.77076065366552E9</v>
@@ -8593,7 +8645,7 @@
         <v>15</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D66" s="1">
         <v>1.77076065674963E9</v>
@@ -8628,7 +8680,7 @@
         <v>14</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D68" s="1">
         <v>1.77076067967062E9</v>
@@ -8644,7 +8696,7 @@
         <v>15</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D69" s="1">
         <v>1.7707606841107E9</v>
@@ -8679,7 +8731,7 @@
         <v>14</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D71" s="1">
         <v>1.77076070601151E9</v>
@@ -8695,7 +8747,7 @@
         <v>15</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D72" s="1">
         <v>1.77076070849159E9</v>
@@ -8730,7 +8782,7 @@
         <v>14</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D74" s="1">
         <v>1.77076072901257E9</v>
@@ -8746,7 +8798,7 @@
         <v>15</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D75" s="1">
         <v>1.77076073185228E9</v>
@@ -8781,7 +8833,7 @@
         <v>14</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D77" s="1">
         <v>1.77076075287306E9</v>
@@ -8797,7 +8849,7 @@
         <v>15</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D78" s="1">
         <v>1.77076075503312E9</v>
@@ -8832,7 +8884,7 @@
         <v>14</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D80" s="1">
         <v>1.77076081645007E9</v>
@@ -8848,7 +8900,7 @@
         <v>15</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D81" s="1">
         <v>1.77076081966998E9</v>
@@ -8883,7 +8935,7 @@
         <v>14</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D83" s="1">
         <v>1.77076088971721E9</v>
@@ -8899,7 +8951,7 @@
         <v>15</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D84" s="1">
         <v>1.77076089295656E9</v>
@@ -8934,7 +8986,7 @@
         <v>14</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D86" s="1">
         <v>1.77076092783232E9</v>
@@ -8950,7 +9002,7 @@
         <v>15</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D87" s="1">
         <v>1.77076093003245E9</v>
@@ -8985,7 +9037,7 @@
         <v>14</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D89" s="1">
         <v>1.77076100439885E9</v>
@@ -9001,7 +9053,7 @@
         <v>15</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D90" s="1">
         <v>1.77076100745897E9</v>
@@ -9036,7 +9088,7 @@
         <v>14</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D92" s="1">
         <v>1.77076103109608E9</v>
@@ -9052,7 +9104,7 @@
         <v>15</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D93" s="1">
         <v>1.77076103373896E9</v>
@@ -9087,7 +9139,7 @@
         <v>14</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D95" s="1">
         <v>1.77076105599936E9</v>
@@ -9103,7 +9155,7 @@
         <v>15</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D96" s="1">
         <v>1.77076105845936E9</v>
@@ -9142,7 +9194,7 @@
         <v>14</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D98" s="1">
         <v>1.77076107763952E9</v>
@@ -9160,7 +9212,7 @@
         <v>15</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D99" s="1">
         <v>1.77076108015959E9</v>
@@ -9199,7 +9251,7 @@
         <v>14</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D101" s="1">
         <v>1.77076110246019E9</v>
@@ -9217,7 +9269,7 @@
         <v>15</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D102" s="1">
         <v>1.77076110455493E9</v>
@@ -9256,7 +9308,7 @@
         <v>14</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D104" s="1">
         <v>1.77076115268054E9</v>
@@ -9274,7 +9326,7 @@
         <v>15</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D105" s="23">
         <v>1.77076115752053E9</v>
@@ -9313,7 +9365,7 @@
         <v>14</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D107" s="1">
         <v>1.77076118008072E9</v>
@@ -9331,7 +9383,7 @@
         <v>15</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D108" s="1">
         <v>1.77076118254112E9</v>
@@ -9368,7 +9420,7 @@
         <v>14</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D110" s="1">
         <v>1.77076121985653E9</v>
@@ -9384,7 +9436,7 @@
         <v>15</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D111" s="1">
         <v>1.77076122194129E9</v>
@@ -9397,17 +9449,17 @@
     </row>
     <row r="112">
       <c r="A112" s="27" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J112" s="28"/>
       <c r="K112" s="29"/>
     </row>
     <row r="113">
       <c r="A113" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>17</v>
@@ -9428,7 +9480,7 @@
         <v>14</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D114" s="1">
         <v>1.75682453697133E9</v>
@@ -9440,7 +9492,7 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>17</v>
@@ -9461,7 +9513,7 @@
         <v>14</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D116" s="1">
         <v>1.75682459695601E9</v>
@@ -9473,7 +9525,7 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>17</v>
@@ -9488,7 +9540,7 @@
         <v>0.8149010226</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="J117" s="28"/>
     </row>
@@ -9497,7 +9549,7 @@
         <v>14</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D118" s="1">
         <v>1.75682491949485E9</v>
@@ -9509,7 +9561,7 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>17</v>
@@ -9530,7 +9582,7 @@
         <v>14</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D120" s="1">
         <v>1.75682511334174E9</v>
@@ -9542,7 +9594,7 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>17</v>
@@ -9563,7 +9615,7 @@
         <v>14</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D122" s="1">
         <v>1.75682518191662E9</v>
@@ -9575,7 +9627,7 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>17</v>
@@ -9590,7 +9642,7 @@
         <v>0.62830973</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="J123" s="28"/>
     </row>
@@ -9599,7 +9651,7 @@
         <v>14</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D124" s="1">
         <v>1.75682521977721E9</v>
@@ -9611,7 +9663,7 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>17</v>
@@ -9632,7 +9684,7 @@
         <v>14</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D126" s="1">
         <v>1.75682527266464E9</v>
@@ -9644,7 +9696,7 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>17</v>
@@ -9665,7 +9717,7 @@
         <v>14</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D128" s="1">
         <v>1.75682534486518E9</v>
@@ -9677,7 +9729,7 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>17</v>
@@ -9698,7 +9750,7 @@
         <v>14</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D130" s="1">
         <v>1.75682538541891E9</v>
@@ -9710,7 +9762,7 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>17</v>
@@ -9731,7 +9783,7 @@
         <v>14</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D132" s="1">
         <v>1.75682541676466E9</v>
@@ -9743,7 +9795,7 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>17</v>
@@ -9764,7 +9816,7 @@
         <v>14</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D134" s="1">
         <v>1.75682547658597E9</v>
@@ -9776,7 +9828,7 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>17</v>
@@ -9797,7 +9849,7 @@
         <v>14</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D136" s="1">
         <v>1.75682550954696E9</v>
@@ -9809,7 +9861,7 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>17</v>
@@ -9830,7 +9882,7 @@
         <v>14</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D138" s="1">
         <v>1.75682558088333E9</v>
@@ -9842,7 +9894,7 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>17</v>
@@ -9863,7 +9915,7 @@
         <v>14</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D140" s="1">
         <v>1.75682575996662E9</v>
@@ -9875,7 +9927,7 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>17</v>
@@ -9896,7 +9948,7 @@
         <v>14</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D142" s="1">
         <v>1.75682582750963E9</v>
@@ -9908,7 +9960,7 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>17</v>
@@ -9929,7 +9981,7 @@
         <v>14</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D144" s="1">
         <v>1.75682591161417E9</v>
@@ -9941,7 +9993,7 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>17</v>
@@ -9956,7 +10008,7 @@
         <v>0.7589043801</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="J145" s="28"/>
     </row>
@@ -9965,7 +10017,7 @@
         <v>14</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D146" s="1">
         <v>1.75682594641469E9</v>
@@ -9977,7 +10029,7 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>17</v>
@@ -9998,7 +10050,7 @@
         <v>14</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D148" s="1">
         <v>1.75682597667404E9</v>
@@ -10010,7 +10062,7 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>17</v>
@@ -10031,7 +10083,7 @@
         <v>14</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D150" s="1">
         <v>1.75682602709609E9</v>
@@ -10043,7 +10095,7 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>17</v>
@@ -10064,7 +10116,7 @@
         <v>14</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D152" s="1">
         <v>1.75682607151843E9</v>
